--- a/events/Pau_2017_WCH/Pau_2017_WCH_start.xlsx
+++ b/events/Pau_2017_WCH/Pau_2017_WCH_start.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W849"/>
+  <dimension ref="A1:AC849"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,17 +519,47 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Name4</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Name5</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Name6</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>ICF_ID1</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ICF_ID2</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ICF_ID3</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ICF_ID4</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ICF_ID5</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ICF_ID6</t>
         </is>
       </c>
     </row>
@@ -878,17 +908,17 @@
           <t>LAVIOLETTE Yannick</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>57783</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>43343</t>
         </is>
@@ -966,17 +996,17 @@
           <t>CHIARELLO Gelindo</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>39956</t>
         </is>
@@ -1054,17 +1084,17 @@
           <t>HIGGINS Shaun</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>42081</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>36655</t>
         </is>
@@ -1132,17 +1162,17 @@
           <t>SZCZEPANSKI Piotr</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>53636</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
@@ -1220,17 +1250,17 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>51872</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>35038</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -1308,17 +1338,17 @@
           <t>CURCEL Leonardo</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
@@ -1396,17 +1426,17 @@
           <t>LONG Tren</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>57124</t>
         </is>
@@ -1484,17 +1514,17 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>51890</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -1572,17 +1602,17 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -1660,12 +1690,12 @@
           <t>KHRAMTSOV Dmitrii</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>35457</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>54800</t>
         </is>
@@ -1743,17 +1773,17 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -1831,17 +1861,17 @@
           <t>MARZO Daniel</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
@@ -1919,17 +1949,17 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -2007,17 +2037,17 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -2095,17 +2125,17 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -2183,17 +2213,17 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -2271,17 +2301,17 @@
           <t>WILLIAMS Courtney</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>51859</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>68771</t>
         </is>
@@ -2359,17 +2389,17 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>35438</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -2447,17 +2477,17 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>35542</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -2535,17 +2565,17 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -2623,12 +2653,12 @@
           <t>JACOBI Seu</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>39209</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>71336</t>
         </is>
@@ -2706,17 +2736,17 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -2794,17 +2824,17 @@
           <t>ITO Yoshika</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>36647</t>
         </is>
@@ -2882,17 +2912,17 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -2970,17 +3000,17 @@
           <t>GOIKOETXEA Irati</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
@@ -3058,17 +3088,17 @@
           <t>YAN Jiahua</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>52023</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>68810</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>43545</t>
         </is>
@@ -3146,17 +3176,17 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -3234,12 +3264,12 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -3317,17 +3347,17 @@
           <t>MINTALOVA Eliska</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="Z36" t="inlineStr">
         <is>
           <t>56169</t>
         </is>
@@ -3405,17 +3435,17 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -3493,17 +3523,17 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>35231</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -3581,17 +3611,17 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -3669,17 +3699,17 @@
           <t>HILGERTOVA Amalie</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>36113</t>
         </is>
@@ -3757,14 +3787,19 @@
           <t>JODAR Celia</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>69447</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>75631</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>36936</t>
         </is>
       </c>
     </row>
@@ -3830,14 +3865,19 @@
           <t>SEPRENYI Sara Timea</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>69570</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>52211</t>
         </is>
       </c>
     </row>
@@ -3913,17 +3953,17 @@
           <t>FONSECA DIAZ Axel</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>41634</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>41635</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>82536</t>
         </is>
@@ -4001,17 +4041,17 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -4089,17 +4129,17 @@
           <t>SLEEBUS Axel</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>35336</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>42892</t>
         </is>
@@ -4177,17 +4217,17 @@
           <t>ZLATAROV Aleksandar</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>35581</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>66066</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>43799</t>
         </is>
@@ -4265,17 +4305,17 @@
           <t>LAUNAY Antoine</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>35482</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>71976</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>68776</t>
         </is>
@@ -4353,17 +4393,17 @@
           <t>BAK Jaehyeong</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>64855</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>82545</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>66073</t>
         </is>
@@ -4441,12 +4481,12 @@
           <t>MERRITT Jaxon</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="Y49" t="inlineStr">
         <is>
           <t>36536</t>
         </is>
@@ -4524,17 +4564,17 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -4612,7 +4652,7 @@
           <t>MAYMISTOV Sergey</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -4690,17 +4730,17 @@
           <t>CORTEZ Geronimo</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>51835</t>
         </is>
@@ -4778,12 +4818,12 @@
           <t>SOARES Renan</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>38015</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>42776</t>
         </is>
@@ -4861,17 +4901,17 @@
           <t>DAWSON Mike</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>36656</t>
         </is>
@@ -4949,17 +4989,17 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>51919</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -5037,17 +5077,17 @@
           <t>WEGER Jakob</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>54909</t>
         </is>
@@ -5115,17 +5155,17 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>35532</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -5203,17 +5243,17 @@
           <t>WEGER Matthias</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>68837</t>
         </is>
@@ -5291,17 +5331,17 @@
           <t>YUAN Tao</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>62343</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="Y59" t="inlineStr">
         <is>
           <t>75492</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>42241</t>
         </is>
@@ -5379,17 +5419,17 @@
           <t>JAKSE Zan</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>44340</t>
         </is>
@@ -5467,17 +5507,17 @@
           <t>CHIARELLO Gelindo</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="W61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>39956</t>
         </is>
@@ -5555,17 +5595,17 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -5643,17 +5683,17 @@
           <t>COMBOT Sebastien</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>35234</t>
         </is>
@@ -5718,7 +5758,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>SCHUBERT Sebastian</t>
+          <t>ICF CANOE SLALOM</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
@@ -5731,17 +5771,12 @@
           <t>SCHWEIKERT Fabian</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>35114</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
       </c>
-      <c r="W64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>38412</t>
         </is>
@@ -5819,17 +5854,17 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr">
+      <c r="Y65" t="inlineStr">
         <is>
           <t>52010</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -5907,17 +5942,17 @@
           <t>MALEK Andrej</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
       </c>
-      <c r="W66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>39246</t>
         </is>
@@ -5995,17 +6030,17 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr">
+      <c r="Y67" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
       </c>
-      <c r="W67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -6083,17 +6118,17 @@
           <t>XU Yanru</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr">
+      <c r="Y68" t="inlineStr">
         <is>
           <t>72213</t>
         </is>
       </c>
-      <c r="W68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>63801</t>
         </is>
@@ -6171,17 +6206,17 @@
           <t>MACEKOVA Simona</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>53078</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr">
+      <c r="Y69" t="inlineStr">
         <is>
           <t>55166</t>
         </is>
       </c>
-      <c r="W69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
@@ -6259,17 +6294,17 @@
           <t>SATO Ayano</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr">
+      <c r="Y70" t="inlineStr">
         <is>
           <t>37756</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>60374</t>
         </is>
@@ -6347,12 +6382,12 @@
           <t>MINAZOVA Alsu</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr">
+      <c r="Y71" t="inlineStr">
         <is>
           <t>35768</t>
         </is>
@@ -6430,17 +6465,17 @@
           <t>OHMAYER Birgit</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
       </c>
-      <c r="V72" t="inlineStr">
+      <c r="Y72" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
       </c>
-      <c r="W72" t="inlineStr">
+      <c r="Z72" t="inlineStr">
         <is>
           <t>39157</t>
         </is>
@@ -6518,17 +6553,17 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
       </c>
-      <c r="V73" t="inlineStr">
+      <c r="Y73" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -6606,17 +6641,17 @@
           <t>VAN DER KNIJFF Annebel</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
       </c>
-      <c r="V74" t="inlineStr">
+      <c r="Y74" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
       </c>
-      <c r="W74" t="inlineStr">
+      <c r="Z74" t="inlineStr">
         <is>
           <t>39945</t>
         </is>
@@ -6694,17 +6729,17 @@
           <t>GIBSON Eilidh</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
       </c>
-      <c r="V75" t="inlineStr">
+      <c r="Y75" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
       </c>
-      <c r="W75" t="inlineStr">
+      <c r="Z75" t="inlineStr">
         <is>
           <t>36708</t>
         </is>
@@ -6782,12 +6817,12 @@
           <t>RIHOVA Eva</t>
         </is>
       </c>
-      <c r="V76" t="inlineStr">
+      <c r="Y76" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
       </c>
-      <c r="W76" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>51791</t>
         </is>
@@ -6865,17 +6900,17 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
       </c>
-      <c r="V77" t="inlineStr">
+      <c r="Y77" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr">
+      <c r="Z77" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -6940,17 +6975,62 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>SKANTAR Ladislav/SKANTAR Peter</t>
+          <t>SKANTAR Ladislav</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>KUCERA Tomas/BATIK Jan</t>
+          <t>SKANTAR Peter</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>HOCHSCHORNER Pavol/HOCHSCHORNER Peter</t>
+          <t>KUCERA Tomas</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>BATIK Jan</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>HOCHSCHORNER Pavol</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>HOCHSCHORNER Peter</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>35360</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>35361</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>35368</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>35367</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>35356</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>35357</t>
         </is>
       </c>
     </row>
@@ -7013,17 +7093,62 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>KARLOVSKY Ondrej/JANE Jakub</t>
+          <t>KARLOVSKY Ondrej</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>KASPAR Jonas/SINDLER Marek</t>
+          <t>JANE Jakub</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>KOPLIK Tomas/VRZAN Jakub</t>
+          <t>KASPAR Jonas</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SINDLER Marek</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>KOPLIK Tomas</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>VRZAN Jakub</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>35060</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>35061</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>35062</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>35063</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>35042</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>35043</t>
         </is>
       </c>
     </row>
@@ -7086,17 +7211,62 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>BEHLING Robert/BECKER Thomas</t>
+          <t>BEHLING Robert</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>MUELLER Kai/MUELLER Kevin</t>
+          <t>BECKER Thomas</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>ANTON Franz/BENZIEN Jan</t>
+          <t>MUELLER Kai</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>MUELLER Kevin</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>ANTON Franz</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>BENZIEN Jan</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>35139</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>35143</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>35148</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>35149</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>35137</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>35134</t>
         </is>
       </c>
     </row>
@@ -7159,17 +7329,62 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>KLAUSS Gauthier/PECHE Matthieu</t>
+          <t>KLAUSS Gauthier</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>SCIANIMANICO Nicolas/CAILHOL Hugo</t>
+          <t>PECHE Matthieu</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>PICCO Pierre/BISO Hugo</t>
+          <t>SCIANIMANICO Nicolas</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>CAILHOL Hugo</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>PICCO Pierre</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>BISO Hugo</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>35350</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>35400</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>35476</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>35491</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>35403</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>35229</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7705,7 @@
           <t>CASTRO PEREIRA Brais</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>51851</t>
         </is>
@@ -7611,12 +7826,12 @@
           <t>HOCHSCHORNER Peter</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
+      <c r="X89" t="inlineStr">
         <is>
           <t>35356</t>
         </is>
       </c>
-      <c r="V89" t="inlineStr">
+      <c r="Y89" t="inlineStr">
         <is>
           <t>35357</t>
         </is>
@@ -7679,12 +7894,12 @@
           <t>PEREZ Jesus</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
       </c>
-      <c r="V90" t="inlineStr">
+      <c r="Y90" t="inlineStr">
         <is>
           <t>36091</t>
         </is>
@@ -7747,12 +7962,12 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr">
+      <c r="X91" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="V91" t="inlineStr">
+      <c r="Y91" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -7815,12 +8030,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V92" t="inlineStr">
+      <c r="Y92" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -7883,12 +8098,12 @@
           <t>MUELLER Kevin</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
+      <c r="X93" t="inlineStr">
         <is>
           <t>35148</t>
         </is>
       </c>
-      <c r="V93" t="inlineStr">
+      <c r="Y93" t="inlineStr">
         <is>
           <t>35149</t>
         </is>
@@ -7951,12 +8166,12 @@
           <t>FERRARI Niccolo</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
+      <c r="X94" t="inlineStr">
         <is>
           <t>35497</t>
         </is>
       </c>
-      <c r="V94" t="inlineStr">
+      <c r="Y94" t="inlineStr">
         <is>
           <t>35498</t>
         </is>
@@ -8019,12 +8234,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="X95" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V95" t="inlineStr">
+      <c r="Y95" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -8087,12 +8302,12 @@
           <t>SZCZEPANSKI Piotr</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
       </c>
-      <c r="V96" t="inlineStr">
+      <c r="Y96" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
@@ -8155,12 +8370,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V97" t="inlineStr">
+      <c r="Y97" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -8223,12 +8438,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="X98" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V98" t="inlineStr">
+      <c r="Y98" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -8291,12 +8506,12 @@
           <t>CAILHOL Hugo</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>35476</t>
         </is>
       </c>
-      <c r="V99" t="inlineStr">
+      <c r="Y99" t="inlineStr">
         <is>
           <t>35491</t>
         </is>
@@ -8359,12 +8574,12 @@
           <t>BENZIEN Jan</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
       </c>
-      <c r="V100" t="inlineStr">
+      <c r="Y100" t="inlineStr">
         <is>
           <t>35134</t>
         </is>
@@ -8427,12 +8642,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr">
+      <c r="X101" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V101" t="inlineStr">
+      <c r="Y101" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -8495,12 +8710,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V102" t="inlineStr">
+      <c r="Y102" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -8563,12 +8778,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
+      <c r="X103" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V103" t="inlineStr">
+      <c r="Y103" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -8631,12 +8846,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
+      <c r="X104" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V104" t="inlineStr">
+      <c r="Y104" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -8694,7 +8909,7 @@
           <t>XU Yanru</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
+      <c r="X105" t="inlineStr">
         <is>
           <t>63801</t>
         </is>
@@ -8752,7 +8967,7 @@
           <t>KONDRATENKO Xeniya</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
+      <c r="X106" t="inlineStr">
         <is>
           <t>42152</t>
         </is>
@@ -8810,7 +9025,7 @@
           <t>ZHANG Jinjie</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
+      <c r="X107" t="inlineStr">
         <is>
           <t>72213</t>
         </is>
@@ -8868,7 +9083,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
+      <c r="X108" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -8926,7 +9141,7 @@
           <t>CHEN Wei-Han</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
+      <c r="X109" t="inlineStr">
         <is>
           <t>61630</t>
         </is>
@@ -9037,7 +9252,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
+      <c r="X111" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -9095,7 +9310,7 @@
           <t>DUANGLAWA Atcharaporn</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr">
+      <c r="X112" t="inlineStr">
         <is>
           <t>61799</t>
         </is>
@@ -9153,7 +9368,7 @@
           <t>SATO Ayano</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
+      <c r="X113" t="inlineStr">
         <is>
           <t>60374</t>
         </is>
@@ -9211,7 +9426,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
+      <c r="X114" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -9269,7 +9484,7 @@
           <t>TRAVERS Kelly</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
+      <c r="X115" t="inlineStr">
         <is>
           <t>51643</t>
         </is>
@@ -9327,7 +9542,7 @@
           <t>O'FERRALL Caoimhe</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
+      <c r="X116" t="inlineStr">
         <is>
           <t>61007</t>
         </is>
@@ -9385,7 +9600,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr">
+      <c r="X117" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -9443,7 +9658,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
+      <c r="X118" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -9501,7 +9716,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
+      <c r="X119" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -9559,7 +9774,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
+      <c r="X120" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -9617,7 +9832,7 @@
           <t>YAGI Airi</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
+      <c r="X121" t="inlineStr">
         <is>
           <t>37756</t>
         </is>
@@ -9675,7 +9890,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
+      <c r="X122" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -9839,7 +10054,7 @@
           <t>RIHOVA Eva</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
+      <c r="X125" t="inlineStr">
         <is>
           <t>51791</t>
         </is>
@@ -9897,7 +10112,7 @@
           <t>KOZOROG Alja</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
+      <c r="X126" t="inlineStr">
         <is>
           <t>39986</t>
         </is>
@@ -9955,7 +10170,7 @@
           <t>SKACHOVA Monika</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
+      <c r="X127" t="inlineStr">
         <is>
           <t>53078</t>
         </is>
@@ -10013,7 +10228,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr">
+      <c r="X128" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -10071,7 +10286,7 @@
           <t>GLEJTEKOVA Simona</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr">
+      <c r="X129" t="inlineStr">
         <is>
           <t>55166</t>
         </is>
@@ -10182,7 +10397,7 @@
           <t>OHMAYER Birgit</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
+      <c r="X131" t="inlineStr">
         <is>
           <t>39157</t>
         </is>
@@ -10240,7 +10455,7 @@
           <t>BIZJAK Nina</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
+      <c r="X132" t="inlineStr">
         <is>
           <t>39984</t>
         </is>
@@ -10298,7 +10513,7 @@
           <t>SABITOVA Zulfia</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
+      <c r="X133" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -10356,7 +10571,7 @@
           <t>MACEKOVA Simona</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
+      <c r="X134" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
@@ -10414,7 +10629,7 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
+      <c r="X135" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -10472,7 +10687,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
+      <c r="X136" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -10530,7 +10745,7 @@
           <t>VAN DER KNIJFF Annebel</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
+      <c r="X137" t="inlineStr">
         <is>
           <t>39945</t>
         </is>
@@ -10588,7 +10803,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr">
+      <c r="X138" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -10646,7 +10861,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr">
+      <c r="X139" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -10704,7 +10919,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
+      <c r="X140" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -10762,7 +10977,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr">
+      <c r="X141" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -10820,7 +11035,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
+      <c r="X142" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -10878,7 +11093,7 @@
           <t>GIBSON Eilidh</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
+      <c r="X143" t="inlineStr">
         <is>
           <t>36708</t>
         </is>
@@ -10936,7 +11151,7 @@
           <t>MUKHGALEEVA Polina</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr">
+      <c r="X144" t="inlineStr">
         <is>
           <t>35768</t>
         </is>
@@ -10994,7 +11209,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr">
+      <c r="X145" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -11052,7 +11267,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr">
+      <c r="X146" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -11110,7 +11325,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr">
+      <c r="X147" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -11168,7 +11383,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr">
+      <c r="X148" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -11279,7 +11494,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr">
+      <c r="X150" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -11337,7 +11552,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr">
+      <c r="X151" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -11395,7 +11610,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr">
+      <c r="X152" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -11453,7 +11668,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
+      <c r="X153" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -11511,7 +11726,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr">
+      <c r="X154" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -11569,7 +11784,7 @@
           <t>FONSECA DIAZ Axel</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr">
+      <c r="X155" t="inlineStr">
         <is>
           <t>82536</t>
         </is>
@@ -11627,7 +11842,7 @@
           <t>YUAN Tao</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
+      <c r="X156" t="inlineStr">
         <is>
           <t>42241</t>
         </is>
@@ -11685,7 +11900,7 @@
           <t>MIRCHEVSKI Borche</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr">
+      <c r="X157" t="inlineStr">
         <is>
           <t>35581</t>
         </is>
@@ -11743,7 +11958,7 @@
           <t>TAMES Alejandro</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr">
+      <c r="X158" t="inlineStr">
         <is>
           <t>60115</t>
         </is>
@@ -11801,7 +12016,7 @@
           <t>BAE Minwoo</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr">
+      <c r="X159" t="inlineStr">
         <is>
           <t>82545</t>
         </is>
@@ -11859,7 +12074,7 @@
           <t>GRANIZO Luis</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
+      <c r="X160" t="inlineStr">
         <is>
           <t>82442</t>
         </is>
@@ -11917,7 +12132,7 @@
           <t>NAJIB Mohamad Nazrin</t>
         </is>
       </c>
-      <c r="U161" t="inlineStr">
+      <c r="X161" t="inlineStr">
         <is>
           <t>75607</t>
         </is>
@@ -11975,7 +12190,7 @@
           <t>GANIISH Leeroy</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr">
+      <c r="X162" t="inlineStr">
         <is>
           <t>75415</t>
         </is>
@@ -12033,7 +12248,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr">
+      <c r="X163" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -12091,7 +12306,7 @@
           <t>SERDITOV Maksim</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr">
+      <c r="X164" t="inlineStr">
         <is>
           <t>72702</t>
         </is>
@@ -12202,7 +12417,7 @@
           <t>LEE Dongheon</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr">
+      <c r="X166" t="inlineStr">
         <is>
           <t>64855</t>
         </is>
@@ -12260,7 +12475,7 @@
           <t>NEBIOVSKI Enis</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr">
+      <c r="X167" t="inlineStr">
         <is>
           <t>66066</t>
         </is>
@@ -12318,7 +12533,7 @@
           <t>SANDVIK Dag</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr">
+      <c r="X168" t="inlineStr">
         <is>
           <t>61587</t>
         </is>
@@ -12376,7 +12591,7 @@
           <t>ZLATAROV Aleksandar</t>
         </is>
       </c>
-      <c r="U169" t="inlineStr">
+      <c r="X169" t="inlineStr">
         <is>
           <t>43799</t>
         </is>
@@ -12434,7 +12649,7 @@
           <t>KARLIVANS Toms</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr">
+      <c r="X170" t="inlineStr">
         <is>
           <t>52325</t>
         </is>
@@ -12492,7 +12707,7 @@
           <t>CELMINS Ritvars</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
+      <c r="X171" t="inlineStr">
         <is>
           <t>35182</t>
         </is>
@@ -12550,7 +12765,7 @@
           <t>HUANG Cunguang</t>
         </is>
       </c>
-      <c r="U172" t="inlineStr">
+      <c r="X172" t="inlineStr">
         <is>
           <t>75492</t>
         </is>
@@ -12608,7 +12823,7 @@
           <t>RYAN Cade</t>
         </is>
       </c>
-      <c r="U173" t="inlineStr">
+      <c r="X173" t="inlineStr">
         <is>
           <t>37919</t>
         </is>
@@ -12666,7 +12881,7 @@
           <t>GASSOU Mel</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr">
+      <c r="X174" t="inlineStr">
         <is>
           <t>35598</t>
         </is>
@@ -12724,7 +12939,7 @@
           <t>ACAR Mustafa Arda</t>
         </is>
       </c>
-      <c r="U175" t="inlineStr">
+      <c r="X175" t="inlineStr">
         <is>
           <t>73572</t>
         </is>
@@ -12782,7 +12997,7 @@
           <t>BAK Jaehyeong</t>
         </is>
       </c>
-      <c r="U176" t="inlineStr">
+      <c r="X176" t="inlineStr">
         <is>
           <t>66073</t>
         </is>
@@ -12840,7 +13055,7 @@
           <t>TEMIRGALIEV Djanibek</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr">
+      <c r="X177" t="inlineStr">
         <is>
           <t>68797</t>
         </is>
@@ -12898,7 +13113,7 @@
           <t>FLAGEUL Gokul</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
+      <c r="X178" t="inlineStr">
         <is>
           <t>60016</t>
         </is>
@@ -12956,7 +13171,7 @@
           <t>MENDEZ Luis</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr">
+      <c r="X179" t="inlineStr">
         <is>
           <t>41635</t>
         </is>
@@ -13014,7 +13229,7 @@
           <t>ZISEKAS Panagiotis</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr">
+      <c r="X180" t="inlineStr">
         <is>
           <t>64786</t>
         </is>
@@ -13072,7 +13287,7 @@
           <t>CESPEDES PEREZ Arnaldo</t>
         </is>
       </c>
-      <c r="U181" t="inlineStr">
+      <c r="X181" t="inlineStr">
         <is>
           <t>41634</t>
         </is>
@@ -13130,7 +13345,7 @@
           <t>KRIESINGER Ingo</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
+      <c r="X182" t="inlineStr">
         <is>
           <t>35336</t>
         </is>
@@ -13241,7 +13456,7 @@
           <t>NGAMSANGA Paitas</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr">
+      <c r="X184" t="inlineStr">
         <is>
           <t>68857</t>
         </is>
@@ -13299,7 +13514,7 @@
           <t>RACZ Koppany</t>
         </is>
       </c>
-      <c r="U185" t="inlineStr">
+      <c r="X185" t="inlineStr">
         <is>
           <t>69570</t>
         </is>
@@ -13357,7 +13572,7 @@
           <t>ECHEVERRIA OLGUIN Andraz</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr">
+      <c r="X186" t="inlineStr">
         <is>
           <t>41646</t>
         </is>
@@ -13415,7 +13630,7 @@
           <t>KORPES Ren</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr">
+      <c r="X187" t="inlineStr">
         <is>
           <t>39941</t>
         </is>
@@ -13473,7 +13688,7 @@
           <t>ALVARENGA Frederico</t>
         </is>
       </c>
-      <c r="U188" t="inlineStr">
+      <c r="X188" t="inlineStr">
         <is>
           <t>71976</t>
         </is>
@@ -13531,7 +13746,7 @@
           <t>SLEEBUS Axel</t>
         </is>
       </c>
-      <c r="U189" t="inlineStr">
+      <c r="X189" t="inlineStr">
         <is>
           <t>42892</t>
         </is>
@@ -13589,7 +13804,7 @@
           <t>HELLARD Suworna</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
+      <c r="X190" t="inlineStr">
         <is>
           <t>43088</t>
         </is>
@@ -13647,7 +13862,7 @@
           <t>SOUDI Mathis</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
+      <c r="X191" t="inlineStr">
         <is>
           <t>69447</t>
         </is>
@@ -13705,7 +13920,7 @@
           <t>TEAGUE Eoin</t>
         </is>
       </c>
-      <c r="U192" t="inlineStr">
+      <c r="X192" t="inlineStr">
         <is>
           <t>37913</t>
         </is>
@@ -13763,7 +13978,7 @@
           <t>WESTFALL Tyler</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr">
+      <c r="X193" t="inlineStr">
         <is>
           <t>51919</t>
         </is>
@@ -13821,7 +14036,7 @@
           <t>CORTEZ Geronimo</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr">
+      <c r="X194" t="inlineStr">
         <is>
           <t>51835</t>
         </is>
@@ -13879,7 +14094,7 @@
           <t>SOARES Renan</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
+      <c r="X195" t="inlineStr">
         <is>
           <t>42776</t>
         </is>
@@ -13990,7 +14205,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U197" t="inlineStr">
+      <c r="X197" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -14048,7 +14263,7 @@
           <t>FORD David</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
+      <c r="X198" t="inlineStr">
         <is>
           <t>35532</t>
         </is>
@@ -14106,7 +14321,7 @@
           <t>MAPELLI Guilherme</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr">
+      <c r="X199" t="inlineStr">
         <is>
           <t>38015</t>
         </is>
@@ -14164,7 +14379,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr">
+      <c r="X200" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -14222,7 +14437,7 @@
           <t>YOSHIDA Taku</t>
         </is>
       </c>
-      <c r="U201" t="inlineStr">
+      <c r="X201" t="inlineStr">
         <is>
           <t>41611</t>
         </is>
@@ -14280,7 +14495,7 @@
           <t>CHIARELLO Gelindo</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
+      <c r="X202" t="inlineStr">
         <is>
           <t>39956</t>
         </is>
@@ -14391,7 +14606,7 @@
           <t>QUAN Xin</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
+      <c r="X204" t="inlineStr">
         <is>
           <t>62343</t>
         </is>
@@ -14449,7 +14664,7 @@
           <t>TAYLER Michael</t>
         </is>
       </c>
-      <c r="U205" t="inlineStr">
+      <c r="X205" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
@@ -14507,7 +14722,7 @@
           <t>DRAPER Warwick</t>
         </is>
       </c>
-      <c r="U206" t="inlineStr">
+      <c r="X206" t="inlineStr">
         <is>
           <t>36536</t>
         </is>
@@ -14565,7 +14780,7 @@
           <t>WERRO Lukas</t>
         </is>
       </c>
-      <c r="U207" t="inlineStr">
+      <c r="X207" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
@@ -14623,7 +14838,7 @@
           <t>BOWERS Christopher</t>
         </is>
       </c>
-      <c r="U208" t="inlineStr">
+      <c r="X208" t="inlineStr">
         <is>
           <t>52010</t>
         </is>
@@ -14681,7 +14896,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U209" t="inlineStr">
+      <c r="X209" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -14739,7 +14954,7 @@
           <t>WEGER Matthias</t>
         </is>
       </c>
-      <c r="U210" t="inlineStr">
+      <c r="X210" t="inlineStr">
         <is>
           <t>68837</t>
         </is>
@@ -14797,7 +15012,7 @@
           <t>YAZAWA Kazuki</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr">
+      <c r="X211" t="inlineStr">
         <is>
           <t>36482</t>
         </is>
@@ -14855,7 +15070,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U212" t="inlineStr">
+      <c r="X212" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -14913,7 +15128,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U213" t="inlineStr">
+      <c r="X213" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -14971,7 +15186,7 @@
           <t>WEGER Jakob</t>
         </is>
       </c>
-      <c r="U214" t="inlineStr">
+      <c r="X214" t="inlineStr">
         <is>
           <t>54909</t>
         </is>
@@ -15029,7 +15244,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U215" t="inlineStr">
+      <c r="X215" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -15140,7 +15355,7 @@
           <t>SILVA Ivan</t>
         </is>
       </c>
-      <c r="U217" t="inlineStr">
+      <c r="X217" t="inlineStr">
         <is>
           <t>35482</t>
         </is>
@@ -15198,7 +15413,7 @@
           <t>JAKSE Zan</t>
         </is>
       </c>
-      <c r="U218" t="inlineStr">
+      <c r="X218" t="inlineStr">
         <is>
           <t>44340</t>
         </is>
@@ -15256,7 +15471,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U219" t="inlineStr">
+      <c r="X219" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -15314,7 +15529,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U220" t="inlineStr">
+      <c r="X220" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -15372,7 +15587,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr">
+      <c r="X221" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -15430,7 +15645,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr">
+      <c r="X222" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -15488,7 +15703,7 @@
           <t>MALEK Andrej</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
+      <c r="X223" t="inlineStr">
         <is>
           <t>39246</t>
         </is>
@@ -15546,7 +15761,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U224" t="inlineStr">
+      <c r="X224" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -15604,7 +15819,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U225" t="inlineStr">
+      <c r="X225" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -15662,7 +15877,7 @@
           <t>DAWSON Mike</t>
         </is>
       </c>
-      <c r="U226" t="inlineStr">
+      <c r="X226" t="inlineStr">
         <is>
           <t>36656</t>
         </is>
@@ -15720,7 +15935,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U227" t="inlineStr">
+      <c r="X227" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -15778,7 +15993,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U228" t="inlineStr">
+      <c r="X228" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -15889,7 +16104,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U230" t="inlineStr">
+      <c r="X230" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -15947,7 +16162,7 @@
           <t>LAUNAY Antoine</t>
         </is>
       </c>
-      <c r="U231" t="inlineStr">
+      <c r="X231" t="inlineStr">
         <is>
           <t>68776</t>
         </is>
@@ -16005,7 +16220,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U232" t="inlineStr">
+      <c r="X232" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -16063,7 +16278,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U233" t="inlineStr">
+      <c r="X233" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -16121,7 +16336,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U234" t="inlineStr">
+      <c r="X234" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -16179,7 +16394,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U235" t="inlineStr">
+      <c r="X235" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -16237,7 +16452,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U236" t="inlineStr">
+      <c r="X236" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -16295,7 +16510,7 @@
           <t>SCHWEIKERT Fabian</t>
         </is>
       </c>
-      <c r="U237" t="inlineStr">
+      <c r="X237" t="inlineStr">
         <is>
           <t>38412</t>
         </is>
@@ -16353,7 +16568,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U238" t="inlineStr">
+      <c r="X238" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -16411,7 +16626,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U239" t="inlineStr">
+      <c r="X239" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -16469,7 +16684,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
+      <c r="X240" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -16527,7 +16742,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U241" t="inlineStr">
+      <c r="X241" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -16585,7 +16800,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U242" t="inlineStr">
+      <c r="X242" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -16643,7 +16858,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
+      <c r="X243" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -16701,7 +16916,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U244" t="inlineStr">
+      <c r="X244" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -16759,7 +16974,7 @@
           <t>COMBOT Sebastien</t>
         </is>
       </c>
-      <c r="U245" t="inlineStr">
+      <c r="X245" t="inlineStr">
         <is>
           <t>35234</t>
         </is>
@@ -16817,7 +17032,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U246" t="inlineStr">
+      <c r="X246" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -16875,7 +17090,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U247" t="inlineStr">
+      <c r="X247" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -16933,7 +17148,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U248" t="inlineStr">
+      <c r="X248" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -16991,7 +17206,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U249" t="inlineStr">
+      <c r="X249" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -17049,7 +17264,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U250" t="inlineStr">
+      <c r="X250" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -17107,7 +17322,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U251" t="inlineStr">
+      <c r="X251" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -17165,7 +17380,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U252" t="inlineStr">
+      <c r="X252" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -17223,7 +17438,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U253" t="inlineStr">
+      <c r="X253" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -17281,7 +17496,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U254" t="inlineStr">
+      <c r="X254" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -17339,7 +17554,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U255" t="inlineStr">
+      <c r="X255" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -17402,7 +17617,7 @@
           <t>CASTRO PEREIRA Brais</t>
         </is>
       </c>
-      <c r="U256" t="inlineStr">
+      <c r="X256" t="inlineStr">
         <is>
           <t>51851</t>
         </is>
@@ -17465,12 +17680,12 @@
           <t>PEREZ Jesus</t>
         </is>
       </c>
-      <c r="U257" t="inlineStr">
+      <c r="X257" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
       </c>
-      <c r="V257" t="inlineStr">
+      <c r="Y257" t="inlineStr">
         <is>
           <t>36091</t>
         </is>
@@ -17533,12 +17748,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U258" t="inlineStr">
+      <c r="X258" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V258" t="inlineStr">
+      <c r="Y258" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -17596,7 +17811,7 @@
           <t>XU Yanru</t>
         </is>
       </c>
-      <c r="U259" t="inlineStr">
+      <c r="X259" t="inlineStr">
         <is>
           <t>63801</t>
         </is>
@@ -17654,7 +17869,7 @@
           <t>KONDRATENKO Xeniya</t>
         </is>
       </c>
-      <c r="U260" t="inlineStr">
+      <c r="X260" t="inlineStr">
         <is>
           <t>42152</t>
         </is>
@@ -17712,7 +17927,7 @@
           <t>ZHANG Jinjie</t>
         </is>
       </c>
-      <c r="U261" t="inlineStr">
+      <c r="X261" t="inlineStr">
         <is>
           <t>72213</t>
         </is>
@@ -17770,7 +17985,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U262" t="inlineStr">
+      <c r="X262" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -17828,7 +18043,7 @@
           <t>CHEN Wei-Han</t>
         </is>
       </c>
-      <c r="U263" t="inlineStr">
+      <c r="X263" t="inlineStr">
         <is>
           <t>61630</t>
         </is>
@@ -17939,7 +18154,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U265" t="inlineStr">
+      <c r="X265" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -17997,7 +18212,7 @@
           <t>DUANGLAWA Atcharaporn</t>
         </is>
       </c>
-      <c r="U266" t="inlineStr">
+      <c r="X266" t="inlineStr">
         <is>
           <t>61799</t>
         </is>
@@ -18055,7 +18270,7 @@
           <t>SATO Ayano</t>
         </is>
       </c>
-      <c r="U267" t="inlineStr">
+      <c r="X267" t="inlineStr">
         <is>
           <t>60374</t>
         </is>
@@ -18113,7 +18328,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U268" t="inlineStr">
+      <c r="X268" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -18171,7 +18386,7 @@
           <t>TRAVERS Kelly</t>
         </is>
       </c>
-      <c r="U269" t="inlineStr">
+      <c r="X269" t="inlineStr">
         <is>
           <t>51643</t>
         </is>
@@ -18229,7 +18444,7 @@
           <t>O'FERRALL Caoimhe</t>
         </is>
       </c>
-      <c r="U270" t="inlineStr">
+      <c r="X270" t="inlineStr">
         <is>
           <t>61007</t>
         </is>
@@ -18287,7 +18502,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U271" t="inlineStr">
+      <c r="X271" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -18345,7 +18560,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U272" t="inlineStr">
+      <c r="X272" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -18403,7 +18618,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U273" t="inlineStr">
+      <c r="X273" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -18461,7 +18676,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U274" t="inlineStr">
+      <c r="X274" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -18519,7 +18734,7 @@
           <t>YAGI Airi</t>
         </is>
       </c>
-      <c r="U275" t="inlineStr">
+      <c r="X275" t="inlineStr">
         <is>
           <t>37756</t>
         </is>
@@ -18577,7 +18792,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U276" t="inlineStr">
+      <c r="X276" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -18688,7 +18903,7 @@
           <t>KOZOROG Alja</t>
         </is>
       </c>
-      <c r="U278" t="inlineStr">
+      <c r="X278" t="inlineStr">
         <is>
           <t>39986</t>
         </is>
@@ -18746,7 +18961,7 @@
           <t>SKACHOVA Monika</t>
         </is>
       </c>
-      <c r="U279" t="inlineStr">
+      <c r="X279" t="inlineStr">
         <is>
           <t>53078</t>
         </is>
@@ -18804,7 +19019,7 @@
           <t>GLEJTEKOVA Simona</t>
         </is>
       </c>
-      <c r="U280" t="inlineStr">
+      <c r="X280" t="inlineStr">
         <is>
           <t>55166</t>
         </is>
@@ -18915,7 +19130,7 @@
           <t>OHMAYER Birgit</t>
         </is>
       </c>
-      <c r="U282" t="inlineStr">
+      <c r="X282" t="inlineStr">
         <is>
           <t>39157</t>
         </is>
@@ -18973,7 +19188,7 @@
           <t>BIZJAK Nina</t>
         </is>
       </c>
-      <c r="U283" t="inlineStr">
+      <c r="X283" t="inlineStr">
         <is>
           <t>39984</t>
         </is>
@@ -19031,7 +19246,7 @@
           <t>SABITOVA Zulfia</t>
         </is>
       </c>
-      <c r="U284" t="inlineStr">
+      <c r="X284" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -19089,7 +19304,7 @@
           <t>MACEKOVA Simona</t>
         </is>
       </c>
-      <c r="U285" t="inlineStr">
+      <c r="X285" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
@@ -19147,7 +19362,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U286" t="inlineStr">
+      <c r="X286" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -19205,7 +19420,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U287" t="inlineStr">
+      <c r="X287" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -19263,7 +19478,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U288" t="inlineStr">
+      <c r="X288" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -19321,7 +19536,7 @@
           <t>GIBSON Eilidh</t>
         </is>
       </c>
-      <c r="U289" t="inlineStr">
+      <c r="X289" t="inlineStr">
         <is>
           <t>36708</t>
         </is>
@@ -19379,7 +19594,7 @@
           <t>FONSECA DIAZ Axel</t>
         </is>
       </c>
-      <c r="U290" t="inlineStr">
+      <c r="X290" t="inlineStr">
         <is>
           <t>82536</t>
         </is>
@@ -19437,7 +19652,7 @@
           <t>YUAN Tao</t>
         </is>
       </c>
-      <c r="U291" t="inlineStr">
+      <c r="X291" t="inlineStr">
         <is>
           <t>42241</t>
         </is>
@@ -19495,7 +19710,7 @@
           <t>MIRCHEVSKI Borche</t>
         </is>
       </c>
-      <c r="U292" t="inlineStr">
+      <c r="X292" t="inlineStr">
         <is>
           <t>35581</t>
         </is>
@@ -19553,7 +19768,7 @@
           <t>TAMES Alejandro</t>
         </is>
       </c>
-      <c r="U293" t="inlineStr">
+      <c r="X293" t="inlineStr">
         <is>
           <t>60115</t>
         </is>
@@ -19611,7 +19826,7 @@
           <t>BAE Minwoo</t>
         </is>
       </c>
-      <c r="U294" t="inlineStr">
+      <c r="X294" t="inlineStr">
         <is>
           <t>82545</t>
         </is>
@@ -19669,7 +19884,7 @@
           <t>GRANIZO Luis</t>
         </is>
       </c>
-      <c r="U295" t="inlineStr">
+      <c r="X295" t="inlineStr">
         <is>
           <t>82442</t>
         </is>
@@ -19727,7 +19942,7 @@
           <t>NAJIB Mohamad Nazrin</t>
         </is>
       </c>
-      <c r="U296" t="inlineStr">
+      <c r="X296" t="inlineStr">
         <is>
           <t>75607</t>
         </is>
@@ -19785,7 +20000,7 @@
           <t>GANIISH Leeroy</t>
         </is>
       </c>
-      <c r="U297" t="inlineStr">
+      <c r="X297" t="inlineStr">
         <is>
           <t>75415</t>
         </is>
@@ -19843,7 +20058,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U298" t="inlineStr">
+      <c r="X298" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -19901,7 +20116,7 @@
           <t>SERDITOV Maksim</t>
         </is>
       </c>
-      <c r="U299" t="inlineStr">
+      <c r="X299" t="inlineStr">
         <is>
           <t>72702</t>
         </is>
@@ -20012,7 +20227,7 @@
           <t>LEE Dongheon</t>
         </is>
       </c>
-      <c r="U301" t="inlineStr">
+      <c r="X301" t="inlineStr">
         <is>
           <t>64855</t>
         </is>
@@ -20070,7 +20285,7 @@
           <t>NEBIOVSKI Enis</t>
         </is>
       </c>
-      <c r="U302" t="inlineStr">
+      <c r="X302" t="inlineStr">
         <is>
           <t>66066</t>
         </is>
@@ -20128,7 +20343,7 @@
           <t>SANDVIK Dag</t>
         </is>
       </c>
-      <c r="U303" t="inlineStr">
+      <c r="X303" t="inlineStr">
         <is>
           <t>61587</t>
         </is>
@@ -20186,7 +20401,7 @@
           <t>ZLATAROV Aleksandar</t>
         </is>
       </c>
-      <c r="U304" t="inlineStr">
+      <c r="X304" t="inlineStr">
         <is>
           <t>43799</t>
         </is>
@@ -20244,7 +20459,7 @@
           <t>KARLIVANS Toms</t>
         </is>
       </c>
-      <c r="U305" t="inlineStr">
+      <c r="X305" t="inlineStr">
         <is>
           <t>52325</t>
         </is>
@@ -20302,7 +20517,7 @@
           <t>CELMINS Ritvars</t>
         </is>
       </c>
-      <c r="U306" t="inlineStr">
+      <c r="X306" t="inlineStr">
         <is>
           <t>35182</t>
         </is>
@@ -20360,7 +20575,7 @@
           <t>HUANG Cunguang</t>
         </is>
       </c>
-      <c r="U307" t="inlineStr">
+      <c r="X307" t="inlineStr">
         <is>
           <t>75492</t>
         </is>
@@ -20418,7 +20633,7 @@
           <t>RYAN Cade</t>
         </is>
       </c>
-      <c r="U308" t="inlineStr">
+      <c r="X308" t="inlineStr">
         <is>
           <t>37919</t>
         </is>
@@ -20476,7 +20691,7 @@
           <t>GASSOU Mel</t>
         </is>
       </c>
-      <c r="U309" t="inlineStr">
+      <c r="X309" t="inlineStr">
         <is>
           <t>35598</t>
         </is>
@@ -20534,7 +20749,7 @@
           <t>ACAR Mustafa Arda</t>
         </is>
       </c>
-      <c r="U310" t="inlineStr">
+      <c r="X310" t="inlineStr">
         <is>
           <t>73572</t>
         </is>
@@ -20592,7 +20807,7 @@
           <t>BAK Jaehyeong</t>
         </is>
       </c>
-      <c r="U311" t="inlineStr">
+      <c r="X311" t="inlineStr">
         <is>
           <t>66073</t>
         </is>
@@ -20650,7 +20865,7 @@
           <t>TEMIRGALIEV Djanibek</t>
         </is>
       </c>
-      <c r="U312" t="inlineStr">
+      <c r="X312" t="inlineStr">
         <is>
           <t>68797</t>
         </is>
@@ -20708,7 +20923,7 @@
           <t>FLAGEUL Gokul</t>
         </is>
       </c>
-      <c r="U313" t="inlineStr">
+      <c r="X313" t="inlineStr">
         <is>
           <t>60016</t>
         </is>
@@ -20766,7 +20981,7 @@
           <t>MENDEZ Luis</t>
         </is>
       </c>
-      <c r="U314" t="inlineStr">
+      <c r="X314" t="inlineStr">
         <is>
           <t>41635</t>
         </is>
@@ -20824,7 +21039,7 @@
           <t>ZISEKAS Panagiotis</t>
         </is>
       </c>
-      <c r="U315" t="inlineStr">
+      <c r="X315" t="inlineStr">
         <is>
           <t>64786</t>
         </is>
@@ -20882,7 +21097,7 @@
           <t>CESPEDES PEREZ Arnaldo</t>
         </is>
       </c>
-      <c r="U316" t="inlineStr">
+      <c r="X316" t="inlineStr">
         <is>
           <t>41634</t>
         </is>
@@ -20940,7 +21155,7 @@
           <t>KRIESINGER Ingo</t>
         </is>
       </c>
-      <c r="U317" t="inlineStr">
+      <c r="X317" t="inlineStr">
         <is>
           <t>35336</t>
         </is>
@@ -21051,7 +21266,7 @@
           <t>NGAMSANGA Paitas</t>
         </is>
       </c>
-      <c r="U319" t="inlineStr">
+      <c r="X319" t="inlineStr">
         <is>
           <t>68857</t>
         </is>
@@ -21109,7 +21324,7 @@
           <t>RACZ Koppany</t>
         </is>
       </c>
-      <c r="U320" t="inlineStr">
+      <c r="X320" t="inlineStr">
         <is>
           <t>69570</t>
         </is>
@@ -21167,7 +21382,7 @@
           <t>ECHEVERRIA OLGUIN Andraz</t>
         </is>
       </c>
-      <c r="U321" t="inlineStr">
+      <c r="X321" t="inlineStr">
         <is>
           <t>41646</t>
         </is>
@@ -21225,7 +21440,7 @@
           <t>KORPES Ren</t>
         </is>
       </c>
-      <c r="U322" t="inlineStr">
+      <c r="X322" t="inlineStr">
         <is>
           <t>39941</t>
         </is>
@@ -21283,7 +21498,7 @@
           <t>ALVARENGA Frederico</t>
         </is>
       </c>
-      <c r="U323" t="inlineStr">
+      <c r="X323" t="inlineStr">
         <is>
           <t>71976</t>
         </is>
@@ -21341,7 +21556,7 @@
           <t>SLEEBUS Axel</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr">
+      <c r="X324" t="inlineStr">
         <is>
           <t>42892</t>
         </is>
@@ -21399,7 +21614,7 @@
           <t>HELLARD Suworna</t>
         </is>
       </c>
-      <c r="U325" t="inlineStr">
+      <c r="X325" t="inlineStr">
         <is>
           <t>43088</t>
         </is>
@@ -21457,7 +21672,7 @@
           <t>SOUDI Mathis</t>
         </is>
       </c>
-      <c r="U326" t="inlineStr">
+      <c r="X326" t="inlineStr">
         <is>
           <t>69447</t>
         </is>
@@ -21515,7 +21730,7 @@
           <t>TEAGUE Eoin</t>
         </is>
       </c>
-      <c r="U327" t="inlineStr">
+      <c r="X327" t="inlineStr">
         <is>
           <t>37913</t>
         </is>
@@ -21573,7 +21788,7 @@
           <t>WESTFALL Tyler</t>
         </is>
       </c>
-      <c r="U328" t="inlineStr">
+      <c r="X328" t="inlineStr">
         <is>
           <t>51919</t>
         </is>
@@ -21631,7 +21846,7 @@
           <t>CORTEZ Geronimo</t>
         </is>
       </c>
-      <c r="U329" t="inlineStr">
+      <c r="X329" t="inlineStr">
         <is>
           <t>51835</t>
         </is>
@@ -21689,7 +21904,7 @@
           <t>SOARES Renan</t>
         </is>
       </c>
-      <c r="U330" t="inlineStr">
+      <c r="X330" t="inlineStr">
         <is>
           <t>42776</t>
         </is>
@@ -21800,7 +22015,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U332" t="inlineStr">
+      <c r="X332" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -21858,7 +22073,7 @@
           <t>FORD David</t>
         </is>
       </c>
-      <c r="U333" t="inlineStr">
+      <c r="X333" t="inlineStr">
         <is>
           <t>35532</t>
         </is>
@@ -21916,7 +22131,7 @@
           <t>MAPELLI Guilherme</t>
         </is>
       </c>
-      <c r="U334" t="inlineStr">
+      <c r="X334" t="inlineStr">
         <is>
           <t>38015</t>
         </is>
@@ -21974,7 +22189,7 @@
           <t>WAHLEN Fredrik</t>
         </is>
       </c>
-      <c r="U335" t="inlineStr">
+      <c r="X335" t="inlineStr">
         <is>
           <t>35102</t>
         </is>
@@ -22032,7 +22247,7 @@
           <t>YOSHIDA Taku</t>
         </is>
       </c>
-      <c r="U336" t="inlineStr">
+      <c r="X336" t="inlineStr">
         <is>
           <t>41611</t>
         </is>
@@ -22090,7 +22305,7 @@
           <t>CHIARELLO Gelindo</t>
         </is>
       </c>
-      <c r="U337" t="inlineStr">
+      <c r="X337" t="inlineStr">
         <is>
           <t>39956</t>
         </is>
@@ -22201,7 +22416,7 @@
           <t>QUAN Xin</t>
         </is>
       </c>
-      <c r="U339" t="inlineStr">
+      <c r="X339" t="inlineStr">
         <is>
           <t>62343</t>
         </is>
@@ -22259,7 +22474,7 @@
           <t>TAYLER Michael</t>
         </is>
       </c>
-      <c r="U340" t="inlineStr">
+      <c r="X340" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
@@ -22317,7 +22532,7 @@
           <t>DRAPER Warwick</t>
         </is>
       </c>
-      <c r="U341" t="inlineStr">
+      <c r="X341" t="inlineStr">
         <is>
           <t>36536</t>
         </is>
@@ -22375,7 +22590,7 @@
           <t>WERRO Lukas</t>
         </is>
       </c>
-      <c r="U342" t="inlineStr">
+      <c r="X342" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
@@ -22433,7 +22648,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U343" t="inlineStr">
+      <c r="X343" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -22491,7 +22706,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U344" t="inlineStr">
+      <c r="X344" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -22549,7 +22764,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U345" t="inlineStr">
+      <c r="X345" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -22660,7 +22875,7 @@
           <t>SILVA Ivan</t>
         </is>
       </c>
-      <c r="U347" t="inlineStr">
+      <c r="X347" t="inlineStr">
         <is>
           <t>35482</t>
         </is>
@@ -22718,7 +22933,7 @@
           <t>JAKSE Zan</t>
         </is>
       </c>
-      <c r="U348" t="inlineStr">
+      <c r="X348" t="inlineStr">
         <is>
           <t>44340</t>
         </is>
@@ -22776,7 +22991,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U349" t="inlineStr">
+      <c r="X349" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -22834,7 +23049,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U350" t="inlineStr">
+      <c r="X350" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -22892,7 +23107,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U351" t="inlineStr">
+      <c r="X351" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -22950,7 +23165,7 @@
           <t>LAUNAY Antoine</t>
         </is>
       </c>
-      <c r="U352" t="inlineStr">
+      <c r="X352" t="inlineStr">
         <is>
           <t>68776</t>
         </is>
@@ -23008,7 +23223,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U353" t="inlineStr">
+      <c r="X353" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -23066,7 +23281,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U354" t="inlineStr">
+      <c r="X354" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -23124,7 +23339,7 @@
           <t>SCHWEIKERT Fabian</t>
         </is>
       </c>
-      <c r="U355" t="inlineStr">
+      <c r="X355" t="inlineStr">
         <is>
           <t>38412</t>
         </is>
@@ -23182,7 +23397,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U356" t="inlineStr">
+      <c r="X356" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -23240,7 +23455,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U357" t="inlineStr">
+      <c r="X357" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -23298,7 +23513,7 @@
           <t>COMBOT Sebastien</t>
         </is>
       </c>
-      <c r="U358" t="inlineStr">
+      <c r="X358" t="inlineStr">
         <is>
           <t>35234</t>
         </is>
@@ -23356,7 +23571,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U359" t="inlineStr">
+      <c r="X359" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -23414,7 +23629,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U360" t="inlineStr">
+      <c r="X360" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -23472,7 +23687,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U361" t="inlineStr">
+      <c r="X361" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -23790,7 +24005,7 @@
           <t>DE UGARTE PUGA Sandra</t>
         </is>
       </c>
-      <c r="U367" t="inlineStr">
+      <c r="X367" t="inlineStr">
         <is>
           <t>82869</t>
         </is>
@@ -23848,7 +24063,7 @@
           <t>YAN Jiahua</t>
         </is>
       </c>
-      <c r="U368" t="inlineStr">
+      <c r="X368" t="inlineStr">
         <is>
           <t>43545</t>
         </is>
@@ -23906,7 +24121,7 @@
           <t>MUZAFFA Marina</t>
         </is>
       </c>
-      <c r="U369" t="inlineStr">
+      <c r="X369" t="inlineStr">
         <is>
           <t>75392</t>
         </is>
@@ -23964,7 +24179,7 @@
           <t>SEPRENYI Sara Timea</t>
         </is>
       </c>
-      <c r="U370" t="inlineStr">
+      <c r="X370" t="inlineStr">
         <is>
           <t>52211</t>
         </is>
@@ -24022,7 +24237,7 @@
           <t>MAENPAA Iisa</t>
         </is>
       </c>
-      <c r="U371" t="inlineStr">
+      <c r="X371" t="inlineStr">
         <is>
           <t>72267</t>
         </is>
@@ -24080,7 +24295,7 @@
           <t>SHRIVASTAVA Jahanvi</t>
         </is>
       </c>
-      <c r="U372" t="inlineStr">
+      <c r="X372" t="inlineStr">
         <is>
           <t>68935</t>
         </is>
@@ -24191,7 +24406,7 @@
           <t>PETROVIC Kristina</t>
         </is>
       </c>
-      <c r="U374" t="inlineStr">
+      <c r="X374" t="inlineStr">
         <is>
           <t>44568</t>
         </is>
@@ -24249,7 +24464,7 @@
           <t>SAETHER Mariann</t>
         </is>
       </c>
-      <c r="U375" t="inlineStr">
+      <c r="X375" t="inlineStr">
         <is>
           <t>53420</t>
         </is>
@@ -24307,7 +24522,7 @@
           <t>RAZEGHIAN Roxana</t>
         </is>
       </c>
-      <c r="U376" t="inlineStr">
+      <c r="X376" t="inlineStr">
         <is>
           <t>63124</t>
         </is>
@@ -24471,7 +24686,7 @@
           <t>PORNCHAI Thatchaporn</t>
         </is>
       </c>
-      <c r="U379" t="inlineStr">
+      <c r="X379" t="inlineStr">
         <is>
           <t>68853</t>
         </is>
@@ -24529,7 +24744,7 @@
           <t>DUANGLAWA Atcharaporn</t>
         </is>
       </c>
-      <c r="U380" t="inlineStr">
+      <c r="X380" t="inlineStr">
         <is>
           <t>61799</t>
         </is>
@@ -24587,7 +24802,7 @@
           <t>MINTALOVA Eliska</t>
         </is>
       </c>
-      <c r="U381" t="inlineStr">
+      <c r="X381" t="inlineStr">
         <is>
           <t>56169</t>
         </is>
@@ -24645,7 +24860,7 @@
           <t>JODAR Celia</t>
         </is>
       </c>
-      <c r="U382" t="inlineStr">
+      <c r="X382" t="inlineStr">
         <is>
           <t>36936</t>
         </is>
@@ -24703,7 +24918,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U383" t="inlineStr">
+      <c r="X383" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -24761,7 +24976,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U384" t="inlineStr">
+      <c r="X384" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -24819,7 +25034,7 @@
           <t>DAVIS Avery</t>
         </is>
       </c>
-      <c r="U385" t="inlineStr">
+      <c r="X385" t="inlineStr">
         <is>
           <t>71336</t>
         </is>
@@ -24877,7 +25092,7 @@
           <t>KONDRATENKO Xeniya</t>
         </is>
       </c>
-      <c r="U386" t="inlineStr">
+      <c r="X386" t="inlineStr">
         <is>
           <t>42152</t>
         </is>
@@ -24935,7 +25150,7 @@
           <t>WILLIAMS Courtney</t>
         </is>
       </c>
-      <c r="U387" t="inlineStr">
+      <c r="X387" t="inlineStr">
         <is>
           <t>68771</t>
         </is>
@@ -24993,7 +25208,7 @@
           <t>RANDLE Kensa</t>
         </is>
       </c>
-      <c r="U388" t="inlineStr">
+      <c r="X388" t="inlineStr">
         <is>
           <t>51859</t>
         </is>
@@ -25051,7 +25266,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U389" t="inlineStr">
+      <c r="X389" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -25109,7 +25324,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U390" t="inlineStr">
+      <c r="X390" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -25167,7 +25382,7 @@
           <t>FAGERLUND Amanda</t>
         </is>
       </c>
-      <c r="U391" t="inlineStr">
+      <c r="X391" t="inlineStr">
         <is>
           <t>43406</t>
         </is>
@@ -25278,7 +25493,7 @@
           <t>IFARRAGUERRI Anna Maria</t>
         </is>
       </c>
-      <c r="U393" t="inlineStr">
+      <c r="X393" t="inlineStr">
         <is>
           <t>39209</t>
         </is>
@@ -25336,7 +25551,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U394" t="inlineStr">
+      <c r="X394" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -25394,7 +25609,7 @@
           <t>ITO Yoshika</t>
         </is>
       </c>
-      <c r="U395" t="inlineStr">
+      <c r="X395" t="inlineStr">
         <is>
           <t>36647</t>
         </is>
@@ -25452,7 +25667,7 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U396" t="inlineStr">
+      <c r="X396" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -25510,7 +25725,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U397" t="inlineStr">
+      <c r="X397" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -25568,7 +25783,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U398" t="inlineStr">
+      <c r="X398" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -25626,7 +25841,7 @@
           <t>GROENEVELD Jessica</t>
         </is>
       </c>
-      <c r="U399" t="inlineStr">
+      <c r="X399" t="inlineStr">
         <is>
           <t>35542</t>
         </is>
@@ -25684,7 +25899,7 @@
           <t>MEDON Joanna</t>
         </is>
       </c>
-      <c r="U400" t="inlineStr">
+      <c r="X400" t="inlineStr">
         <is>
           <t>35438</t>
         </is>
@@ -25742,7 +25957,7 @@
           <t>REN Ye</t>
         </is>
       </c>
-      <c r="U401" t="inlineStr">
+      <c r="X401" t="inlineStr">
         <is>
           <t>68810</t>
         </is>
@@ -25800,7 +26015,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U402" t="inlineStr">
+      <c r="X402" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -25858,7 +26073,7 @@
           <t>GIAI PRON Maria Clara</t>
         </is>
       </c>
-      <c r="U403" t="inlineStr">
+      <c r="X403" t="inlineStr">
         <is>
           <t>35218</t>
         </is>
@@ -25916,7 +26131,7 @@
           <t>LI Tong</t>
         </is>
       </c>
-      <c r="U404" t="inlineStr">
+      <c r="X404" t="inlineStr">
         <is>
           <t>52023</t>
         </is>
@@ -25974,7 +26189,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U405" t="inlineStr">
+      <c r="X405" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -26032,7 +26247,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U406" t="inlineStr">
+      <c r="X406" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -26090,7 +26305,7 @@
           <t>HILGERTOVA Amalie</t>
         </is>
       </c>
-      <c r="U407" t="inlineStr">
+      <c r="X407" t="inlineStr">
         <is>
           <t>36113</t>
         </is>
@@ -26148,7 +26363,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U408" t="inlineStr">
+      <c r="X408" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -26206,7 +26421,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U409" t="inlineStr">
+      <c r="X409" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -26264,7 +26479,7 @@
           <t>GOIKOETXEA Irati</t>
         </is>
       </c>
-      <c r="U410" t="inlineStr">
+      <c r="X410" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
@@ -26322,7 +26537,7 @@
           <t>KALISKA Elena</t>
         </is>
       </c>
-      <c r="U411" t="inlineStr">
+      <c r="X411" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
@@ -26380,7 +26595,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U412" t="inlineStr">
+      <c r="X412" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -26438,7 +26653,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U413" t="inlineStr">
+      <c r="X413" t="inlineStr">
         <is>
           <t>35231</t>
         </is>
@@ -26496,7 +26711,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U414" t="inlineStr">
+      <c r="X414" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -26554,7 +26769,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U415" t="inlineStr">
+      <c r="X415" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -26612,7 +26827,7 @@
           <t>GALUSKOVA Karolina</t>
         </is>
       </c>
-      <c r="U416" t="inlineStr">
+      <c r="X416" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
@@ -26670,7 +26885,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U417" t="inlineStr">
+      <c r="X417" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -26728,7 +26943,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U418" t="inlineStr">
+      <c r="X418" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -26786,7 +27001,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U419" t="inlineStr">
+      <c r="X419" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -26844,7 +27059,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U420" t="inlineStr">
+      <c r="X420" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -26902,7 +27117,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U421" t="inlineStr">
+      <c r="X421" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -26960,7 +27175,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U422" t="inlineStr">
+      <c r="X422" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -27018,7 +27233,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U423" t="inlineStr">
+      <c r="X423" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -27076,7 +27291,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U424" t="inlineStr">
+      <c r="X424" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -27134,7 +27349,7 @@
           <t>LEITNER Lisa</t>
         </is>
       </c>
-      <c r="U425" t="inlineStr">
+      <c r="X425" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
@@ -27192,7 +27407,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U426" t="inlineStr">
+      <c r="X426" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -27250,7 +27465,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U427" t="inlineStr">
+      <c r="X427" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -27308,7 +27523,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U428" t="inlineStr">
+      <c r="X428" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -27366,7 +27581,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U429" t="inlineStr">
+      <c r="X429" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -27424,7 +27639,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U430" t="inlineStr">
+      <c r="X430" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -27482,7 +27697,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U431" t="inlineStr">
+      <c r="X431" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -27540,7 +27755,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U432" t="inlineStr">
+      <c r="X432" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -27598,7 +27813,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U433" t="inlineStr">
+      <c r="X433" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -27656,7 +27871,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U434" t="inlineStr">
+      <c r="X434" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -27714,7 +27929,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U435" t="inlineStr">
+      <c r="X435" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -27772,7 +27987,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U436" t="inlineStr">
+      <c r="X436" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -27830,7 +28045,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U437" t="inlineStr">
+      <c r="X437" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -27888,7 +28103,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U438" t="inlineStr">
+      <c r="X438" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -27946,7 +28161,7 @@
           <t>MAKUBO Sandile</t>
         </is>
       </c>
-      <c r="U439" t="inlineStr">
+      <c r="X439" t="inlineStr">
         <is>
           <t>69119</t>
         </is>
@@ -28004,7 +28219,7 @@
           <t>BERT Michel</t>
         </is>
       </c>
-      <c r="U440" t="inlineStr">
+      <c r="X440" t="inlineStr">
         <is>
           <t>82901</t>
         </is>
@@ -28062,7 +28277,7 @@
           <t>HUMENIUK Vladyslav</t>
         </is>
       </c>
-      <c r="U441" t="inlineStr">
+      <c r="X441" t="inlineStr">
         <is>
           <t>72020</t>
         </is>
@@ -28120,7 +28335,7 @@
           <t>REZANEJAD HASSANJANI Amir</t>
         </is>
       </c>
-      <c r="U442" t="inlineStr">
+      <c r="X442" t="inlineStr">
         <is>
           <t>75398</t>
         </is>
@@ -28178,7 +28393,7 @@
           <t>SARAMANDIF Terence Benjamin</t>
         </is>
       </c>
-      <c r="U443" t="inlineStr">
+      <c r="X443" t="inlineStr">
         <is>
           <t>79340</t>
         </is>
@@ -28236,7 +28451,7 @@
           <t>OZOLS Kriss</t>
         </is>
       </c>
-      <c r="U444" t="inlineStr">
+      <c r="X444" t="inlineStr">
         <is>
           <t>48993</t>
         </is>
@@ -28294,7 +28509,7 @@
           <t>MUSEVYCH Vadym</t>
         </is>
       </c>
-      <c r="U445" t="inlineStr">
+      <c r="X445" t="inlineStr">
         <is>
           <t>35525</t>
         </is>
@@ -28405,7 +28620,7 @@
           <t>CHAKIR Issam</t>
         </is>
       </c>
-      <c r="U447" t="inlineStr">
+      <c r="X447" t="inlineStr">
         <is>
           <t>75631</t>
         </is>
@@ -28463,7 +28678,7 @@
           <t>MAXIMOV Vitaly</t>
         </is>
       </c>
-      <c r="U448" t="inlineStr">
+      <c r="X448" t="inlineStr">
         <is>
           <t>54800</t>
         </is>
@@ -28521,7 +28736,7 @@
           <t>KIM Beomsoo</t>
         </is>
       </c>
-      <c r="U449" t="inlineStr">
+      <c r="X449" t="inlineStr">
         <is>
           <t>64845</t>
         </is>
@@ -28579,7 +28794,7 @@
           <t>ZISEKAS Panagiotis</t>
         </is>
       </c>
-      <c r="U450" t="inlineStr">
+      <c r="X450" t="inlineStr">
         <is>
           <t>64786</t>
         </is>
@@ -28637,7 +28852,7 @@
           <t>AMANBAYEV Adil</t>
         </is>
       </c>
-      <c r="U451" t="inlineStr">
+      <c r="X451" t="inlineStr">
         <is>
           <t>68999</t>
         </is>
@@ -28695,7 +28910,7 @@
           <t>ALVARENGA Frederico</t>
         </is>
       </c>
-      <c r="U452" t="inlineStr">
+      <c r="X452" t="inlineStr">
         <is>
           <t>71976</t>
         </is>
@@ -28753,7 +28968,7 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U453" t="inlineStr">
+      <c r="X453" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -28811,7 +29026,7 @@
           <t>MARZO Daniel</t>
         </is>
       </c>
-      <c r="U454" t="inlineStr">
+      <c r="X454" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
@@ -28869,7 +29084,7 @@
           <t>BOURHIS Yves</t>
         </is>
       </c>
-      <c r="U455" t="inlineStr">
+      <c r="X455" t="inlineStr">
         <is>
           <t>63237</t>
         </is>
@@ -28927,7 +29142,7 @@
           <t>SZCZEPANSKI Piotr</t>
         </is>
       </c>
-      <c r="U456" t="inlineStr">
+      <c r="X456" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
@@ -28985,7 +29200,7 @@
           <t>CHIARELLO Gelindo</t>
         </is>
       </c>
-      <c r="U457" t="inlineStr">
+      <c r="X457" t="inlineStr">
         <is>
           <t>39956</t>
         </is>
@@ -29043,7 +29258,7 @@
           <t>TEMIRGALIEV Alibek</t>
         </is>
       </c>
-      <c r="U458" t="inlineStr">
+      <c r="X458" t="inlineStr">
         <is>
           <t>61158</t>
         </is>
@@ -29101,7 +29316,7 @@
           <t>LAVIOLETTE Yannick</t>
         </is>
       </c>
-      <c r="U459" t="inlineStr">
+      <c r="X459" t="inlineStr">
         <is>
           <t>43343</t>
         </is>
@@ -29159,7 +29374,7 @@
           <t>HIGGINS Shaun</t>
         </is>
       </c>
-      <c r="U460" t="inlineStr">
+      <c r="X460" t="inlineStr">
         <is>
           <t>36655</t>
         </is>
@@ -29217,7 +29432,7 @@
           <t>LONG Tren</t>
         </is>
       </c>
-      <c r="U461" t="inlineStr">
+      <c r="X461" t="inlineStr">
         <is>
           <t>57124</t>
         </is>
@@ -29275,7 +29490,7 @@
           <t>SILVA Jose</t>
         </is>
       </c>
-      <c r="U462" t="inlineStr">
+      <c r="X462" t="inlineStr">
         <is>
           <t>36494</t>
         </is>
@@ -29333,7 +29548,7 @@
           <t>CHAIDET Yutthakan</t>
         </is>
       </c>
-      <c r="U463" t="inlineStr">
+      <c r="X463" t="inlineStr">
         <is>
           <t>51798</t>
         </is>
@@ -29391,7 +29606,7 @@
           <t>KULIKOV Alexandr</t>
         </is>
       </c>
-      <c r="U464" t="inlineStr">
+      <c r="X464" t="inlineStr">
         <is>
           <t>39679</t>
         </is>
@@ -29449,7 +29664,7 @@
           <t>ZHENG Jiaxin</t>
         </is>
       </c>
-      <c r="U465" t="inlineStr">
+      <c r="X465" t="inlineStr">
         <is>
           <t>75381</t>
         </is>
@@ -29507,7 +29722,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U466" t="inlineStr">
+      <c r="X466" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -29565,7 +29780,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U467" t="inlineStr">
+      <c r="X467" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -29623,7 +29838,7 @@
           <t>WASHER Patrick</t>
         </is>
       </c>
-      <c r="U468" t="inlineStr">
+      <c r="X468" t="inlineStr">
         <is>
           <t>42081</t>
         </is>
@@ -29681,7 +29896,7 @@
           <t>POMEROY Spencer</t>
         </is>
       </c>
-      <c r="U469" t="inlineStr">
+      <c r="X469" t="inlineStr">
         <is>
           <t>57783</t>
         </is>
@@ -29739,7 +29954,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U470" t="inlineStr">
+      <c r="X470" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -29797,7 +30012,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U471" t="inlineStr">
+      <c r="X471" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -29855,7 +30070,7 @@
           <t>CURCEL Leonardo</t>
         </is>
       </c>
-      <c r="U472" t="inlineStr">
+      <c r="X472" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
@@ -29913,7 +30128,7 @@
           <t>LHOTA Matyas</t>
         </is>
       </c>
-      <c r="U473" t="inlineStr">
+      <c r="X473" t="inlineStr">
         <is>
           <t>51872</t>
         </is>
@@ -29971,7 +30186,7 @@
           <t>GIBB Benjamin</t>
         </is>
       </c>
-      <c r="U474" t="inlineStr">
+      <c r="X474" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
@@ -30029,7 +30244,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U475" t="inlineStr">
+      <c r="X475" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -30087,7 +30302,7 @@
           <t>SHU Jianming</t>
         </is>
       </c>
-      <c r="U476" t="inlineStr">
+      <c r="X476" t="inlineStr">
         <is>
           <t>47327</t>
         </is>
@@ -30145,7 +30360,7 @@
           <t>CORREA Charles</t>
         </is>
       </c>
-      <c r="U477" t="inlineStr">
+      <c r="X477" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
@@ -30203,7 +30418,7 @@
           <t>SZTUBA Kacper</t>
         </is>
       </c>
-      <c r="U478" t="inlineStr">
+      <c r="X478" t="inlineStr">
         <is>
           <t>53636</t>
         </is>
@@ -30261,7 +30476,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U479" t="inlineStr">
+      <c r="X479" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -30319,7 +30534,7 @@
           <t>CARTER Tristan</t>
         </is>
       </c>
-      <c r="U480" t="inlineStr">
+      <c r="X480" t="inlineStr">
         <is>
           <t>51890</t>
         </is>
@@ -30377,7 +30592,7 @@
           <t>BORGES Felipe</t>
         </is>
       </c>
-      <c r="U481" t="inlineStr">
+      <c r="X481" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
@@ -30435,7 +30650,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U482" t="inlineStr">
+      <c r="X482" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -30493,7 +30708,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U483" t="inlineStr">
+      <c r="X483" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -30551,7 +30766,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U484" t="inlineStr">
+      <c r="X484" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -30609,7 +30824,7 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U485" t="inlineStr">
+      <c r="X485" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -30667,7 +30882,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U486" t="inlineStr">
+      <c r="X486" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -30725,7 +30940,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U487" t="inlineStr">
+      <c r="X487" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -30783,7 +30998,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U488" t="inlineStr">
+      <c r="X488" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -30841,7 +31056,7 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U489" t="inlineStr">
+      <c r="X489" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -30899,7 +31114,7 @@
           <t>SETKIN Kirill</t>
         </is>
       </c>
-      <c r="U490" t="inlineStr">
+      <c r="X490" t="inlineStr">
         <is>
           <t>35457</t>
         </is>
@@ -30957,7 +31172,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U491" t="inlineStr">
+      <c r="X491" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -31015,7 +31230,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U492" t="inlineStr">
+      <c r="X492" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -31073,7 +31288,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U493" t="inlineStr">
+      <c r="X493" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -31131,7 +31346,7 @@
           <t>GEBAS Vitezslav</t>
         </is>
       </c>
-      <c r="U494" t="inlineStr">
+      <c r="X494" t="inlineStr">
         <is>
           <t>35038</t>
         </is>
@@ -31189,7 +31404,7 @@
           <t>BADURA Jergus</t>
         </is>
       </c>
-      <c r="U495" t="inlineStr">
+      <c r="X495" t="inlineStr">
         <is>
           <t>68767</t>
         </is>
@@ -31247,7 +31462,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U496" t="inlineStr">
+      <c r="X496" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -31305,7 +31520,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U497" t="inlineStr">
+      <c r="X497" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -31363,7 +31578,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U498" t="inlineStr">
+      <c r="X498" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -31421,7 +31636,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U499" t="inlineStr">
+      <c r="X499" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -31479,7 +31694,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U500" t="inlineStr">
+      <c r="X500" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -31537,7 +31752,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U501" t="inlineStr">
+      <c r="X501" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -31595,7 +31810,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U502" t="inlineStr">
+      <c r="X502" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -31653,7 +31868,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U503" t="inlineStr">
+      <c r="X503" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -31711,7 +31926,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U504" t="inlineStr">
+      <c r="X504" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -31769,7 +31984,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U505" t="inlineStr">
+      <c r="X505" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -31827,7 +32042,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U506" t="inlineStr">
+      <c r="X506" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -31885,7 +32100,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U507" t="inlineStr">
+      <c r="X507" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -31943,7 +32158,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U508" t="inlineStr">
+      <c r="X508" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -32001,7 +32216,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U509" t="inlineStr">
+      <c r="X509" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -32059,7 +32274,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U510" t="inlineStr">
+      <c r="X510" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -32117,7 +32332,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U511" t="inlineStr">
+      <c r="X511" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -32175,7 +32390,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U512" t="inlineStr">
+      <c r="X512" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -32233,7 +32448,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U513" t="inlineStr">
+      <c r="X513" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -32296,7 +32511,7 @@
           <t>POCHWALA Marcin</t>
         </is>
       </c>
-      <c r="V514" t="inlineStr">
+      <c r="Y514" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
@@ -32359,12 +32574,12 @@
           <t>SHU Jianming</t>
         </is>
       </c>
-      <c r="U515" t="inlineStr">
+      <c r="X515" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
       </c>
-      <c r="V515" t="inlineStr">
+      <c r="Y515" t="inlineStr">
         <is>
           <t>47327</t>
         </is>
@@ -32427,12 +32642,12 @@
           <t>QUEMENEUR Malo</t>
         </is>
       </c>
-      <c r="U516" t="inlineStr">
+      <c r="X516" t="inlineStr">
         <is>
           <t>41566</t>
         </is>
       </c>
-      <c r="V516" t="inlineStr">
+      <c r="Y516" t="inlineStr">
         <is>
           <t>60403</t>
         </is>
@@ -32495,7 +32710,7 @@
           <t>OBRAZTSOV Maxim</t>
         </is>
       </c>
-      <c r="V517" t="inlineStr">
+      <c r="Y517" t="inlineStr">
         <is>
           <t>35767</t>
         </is>
@@ -32558,12 +32773,12 @@
           <t>ROISIN Theo</t>
         </is>
       </c>
-      <c r="U518" t="inlineStr">
+      <c r="X518" t="inlineStr">
         <is>
           <t>78746</t>
         </is>
       </c>
-      <c r="V518" t="inlineStr">
+      <c r="Y518" t="inlineStr">
         <is>
           <t>69010</t>
         </is>
@@ -32626,12 +32841,12 @@
           <t>ZHENG Jiaxin</t>
         </is>
       </c>
-      <c r="U519" t="inlineStr">
+      <c r="X519" t="inlineStr">
         <is>
           <t>63801</t>
         </is>
       </c>
-      <c r="V519" t="inlineStr">
+      <c r="Y519" t="inlineStr">
         <is>
           <t>75381</t>
         </is>
@@ -32694,12 +32909,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U520" t="inlineStr">
+      <c r="X520" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
       </c>
-      <c r="V520" t="inlineStr">
+      <c r="Y520" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -32762,12 +32977,12 @@
           <t>PRIGENT Yves</t>
         </is>
       </c>
-      <c r="U521" t="inlineStr">
+      <c r="X521" t="inlineStr">
         <is>
           <t>51995</t>
         </is>
       </c>
-      <c r="V521" t="inlineStr">
+      <c r="Y521" t="inlineStr">
         <is>
           <t>35671</t>
         </is>
@@ -32830,12 +33045,12 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U522" t="inlineStr">
+      <c r="X522" t="inlineStr">
         <is>
           <t>35498</t>
         </is>
       </c>
-      <c r="V522" t="inlineStr">
+      <c r="Y522" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -32898,12 +33113,12 @@
           <t>MASEK Jan</t>
         </is>
       </c>
-      <c r="U523" t="inlineStr">
+      <c r="X523" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
       </c>
-      <c r="V523" t="inlineStr">
+      <c r="Y523" t="inlineStr">
         <is>
           <t>36013</t>
         </is>
@@ -32966,7 +33181,7 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="V524" t="inlineStr">
+      <c r="Y524" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -33024,7 +33239,7 @@
           <t>DE UGARTE PUGA Sandra</t>
         </is>
       </c>
-      <c r="U525" t="inlineStr">
+      <c r="X525" t="inlineStr">
         <is>
           <t>82869</t>
         </is>
@@ -33082,7 +33297,7 @@
           <t>YAN Jiahua</t>
         </is>
       </c>
-      <c r="U526" t="inlineStr">
+      <c r="X526" t="inlineStr">
         <is>
           <t>43545</t>
         </is>
@@ -33140,7 +33355,7 @@
           <t>MUZAFFA Marina</t>
         </is>
       </c>
-      <c r="U527" t="inlineStr">
+      <c r="X527" t="inlineStr">
         <is>
           <t>75392</t>
         </is>
@@ -33198,7 +33413,7 @@
           <t>SEPRENYI Sara Timea</t>
         </is>
       </c>
-      <c r="U528" t="inlineStr">
+      <c r="X528" t="inlineStr">
         <is>
           <t>52211</t>
         </is>
@@ -33309,7 +33524,7 @@
           <t>SHRIVASTAVA Jahanvi</t>
         </is>
       </c>
-      <c r="U530" t="inlineStr">
+      <c r="X530" t="inlineStr">
         <is>
           <t>68935</t>
         </is>
@@ -33420,7 +33635,7 @@
           <t>PETROVIC Kristina</t>
         </is>
       </c>
-      <c r="U532" t="inlineStr">
+      <c r="X532" t="inlineStr">
         <is>
           <t>44568</t>
         </is>
@@ -33478,7 +33693,7 @@
           <t>SAETHER Mariann</t>
         </is>
       </c>
-      <c r="U533" t="inlineStr">
+      <c r="X533" t="inlineStr">
         <is>
           <t>53420</t>
         </is>
@@ -33536,7 +33751,7 @@
           <t>RAZEGHIAN Roxana</t>
         </is>
       </c>
-      <c r="U534" t="inlineStr">
+      <c r="X534" t="inlineStr">
         <is>
           <t>63124</t>
         </is>
@@ -33700,7 +33915,7 @@
           <t>PORNCHAI Thatchaporn</t>
         </is>
       </c>
-      <c r="U537" t="inlineStr">
+      <c r="X537" t="inlineStr">
         <is>
           <t>68853</t>
         </is>
@@ -33758,7 +33973,7 @@
           <t>DUANGLAWA Atcharaporn</t>
         </is>
       </c>
-      <c r="U538" t="inlineStr">
+      <c r="X538" t="inlineStr">
         <is>
           <t>61799</t>
         </is>
@@ -33816,7 +34031,7 @@
           <t>MINTALOVA Eliska</t>
         </is>
       </c>
-      <c r="U539" t="inlineStr">
+      <c r="X539" t="inlineStr">
         <is>
           <t>56169</t>
         </is>
@@ -33874,7 +34089,7 @@
           <t>JODAR Celia</t>
         </is>
       </c>
-      <c r="U540" t="inlineStr">
+      <c r="X540" t="inlineStr">
         <is>
           <t>36936</t>
         </is>
@@ -33932,7 +34147,7 @@
           <t>BAYLACQ Oceane</t>
         </is>
       </c>
-      <c r="U541" t="inlineStr">
+      <c r="X541" t="inlineStr">
         <is>
           <t>69444</t>
         </is>
@@ -33990,7 +34205,7 @@
           <t>BETTERIDGE Lois</t>
         </is>
       </c>
-      <c r="U542" t="inlineStr">
+      <c r="X542" t="inlineStr">
         <is>
           <t>60078</t>
         </is>
@@ -34048,7 +34263,7 @@
           <t>DAVIS Avery</t>
         </is>
       </c>
-      <c r="U543" t="inlineStr">
+      <c r="X543" t="inlineStr">
         <is>
           <t>71336</t>
         </is>
@@ -34106,7 +34321,7 @@
           <t>KONDRATENKO Xeniya</t>
         </is>
       </c>
-      <c r="U544" t="inlineStr">
+      <c r="X544" t="inlineStr">
         <is>
           <t>42152</t>
         </is>
@@ -34164,7 +34379,7 @@
           <t>WILLIAMS Courtney</t>
         </is>
       </c>
-      <c r="U545" t="inlineStr">
+      <c r="X545" t="inlineStr">
         <is>
           <t>68771</t>
         </is>
@@ -34222,7 +34437,7 @@
           <t>RANDLE Kensa</t>
         </is>
       </c>
-      <c r="U546" t="inlineStr">
+      <c r="X546" t="inlineStr">
         <is>
           <t>51859</t>
         </is>
@@ -34280,7 +34495,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U547" t="inlineStr">
+      <c r="X547" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -34338,7 +34553,7 @@
           <t>ESTACIA NETA Omira</t>
         </is>
       </c>
-      <c r="U548" t="inlineStr">
+      <c r="X548" t="inlineStr">
         <is>
           <t>60494</t>
         </is>
@@ -34396,7 +34611,7 @@
           <t>FAGERLUND Amanda</t>
         </is>
       </c>
-      <c r="U549" t="inlineStr">
+      <c r="X549" t="inlineStr">
         <is>
           <t>43406</t>
         </is>
@@ -34507,7 +34722,7 @@
           <t>IFARRAGUERRI Anna Maria</t>
         </is>
       </c>
-      <c r="U551" t="inlineStr">
+      <c r="X551" t="inlineStr">
         <is>
           <t>39209</t>
         </is>
@@ -34565,7 +34780,7 @@
           <t>MAHEU Florence</t>
         </is>
       </c>
-      <c r="U552" t="inlineStr">
+      <c r="X552" t="inlineStr">
         <is>
           <t>36416</t>
         </is>
@@ -34623,7 +34838,7 @@
           <t>ITO Yoshika</t>
         </is>
       </c>
-      <c r="U553" t="inlineStr">
+      <c r="X553" t="inlineStr">
         <is>
           <t>36647</t>
         </is>
@@ -34681,7 +34896,7 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U554" t="inlineStr">
+      <c r="X554" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -34739,7 +34954,7 @@
           <t>TEUNISSEN Lena</t>
         </is>
       </c>
-      <c r="U555" t="inlineStr">
+      <c r="X555" t="inlineStr">
         <is>
           <t>35344</t>
         </is>
@@ -34797,7 +35012,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U556" t="inlineStr">
+      <c r="X556" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -34855,7 +35070,7 @@
           <t>GROENEVELD Jessica</t>
         </is>
       </c>
-      <c r="U557" t="inlineStr">
+      <c r="X557" t="inlineStr">
         <is>
           <t>35542</t>
         </is>
@@ -34913,7 +35128,7 @@
           <t>MEDON Joanna</t>
         </is>
       </c>
-      <c r="U558" t="inlineStr">
+      <c r="X558" t="inlineStr">
         <is>
           <t>35438</t>
         </is>
@@ -34971,7 +35186,7 @@
           <t>REN Ye</t>
         </is>
       </c>
-      <c r="U559" t="inlineStr">
+      <c r="X559" t="inlineStr">
         <is>
           <t>68810</t>
         </is>
@@ -35029,7 +35244,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U560" t="inlineStr">
+      <c r="X560" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -35087,7 +35302,7 @@
           <t>GIAI PRON Maria Clara</t>
         </is>
       </c>
-      <c r="U561" t="inlineStr">
+      <c r="X561" t="inlineStr">
         <is>
           <t>35218</t>
         </is>
@@ -35145,7 +35360,7 @@
           <t>LI Tong</t>
         </is>
       </c>
-      <c r="U562" t="inlineStr">
+      <c r="X562" t="inlineStr">
         <is>
           <t>52023</t>
         </is>
@@ -35203,7 +35418,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U563" t="inlineStr">
+      <c r="X563" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -35261,7 +35476,7 @@
           <t>HILGERTOVA Amalie</t>
         </is>
       </c>
-      <c r="U564" t="inlineStr">
+      <c r="X564" t="inlineStr">
         <is>
           <t>36113</t>
         </is>
@@ -35319,7 +35534,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U565" t="inlineStr">
+      <c r="X565" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -35377,7 +35592,7 @@
           <t>GOIKOETXEA Irati</t>
         </is>
       </c>
-      <c r="U566" t="inlineStr">
+      <c r="X566" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
@@ -35435,7 +35650,7 @@
           <t>ECKHARDT Kate</t>
         </is>
       </c>
-      <c r="U567" t="inlineStr">
+      <c r="X567" t="inlineStr">
         <is>
           <t>44815</t>
         </is>
@@ -35493,7 +35708,7 @@
           <t>GALUSKOVA Karolina</t>
         </is>
       </c>
-      <c r="U568" t="inlineStr">
+      <c r="X568" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
@@ -35551,7 +35766,7 @@
           <t>MARTINEZ Marta</t>
         </is>
       </c>
-      <c r="U569" t="inlineStr">
+      <c r="X569" t="inlineStr">
         <is>
           <t>35760</t>
         </is>
@@ -35609,7 +35824,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U570" t="inlineStr">
+      <c r="X570" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -35667,7 +35882,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U571" t="inlineStr">
+      <c r="X571" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -35725,7 +35940,7 @@
           <t>LEITNER Lisa</t>
         </is>
       </c>
-      <c r="U572" t="inlineStr">
+      <c r="X572" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
@@ -35783,7 +35998,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U573" t="inlineStr">
+      <c r="X573" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -35841,7 +36056,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U574" t="inlineStr">
+      <c r="X574" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -35899,7 +36114,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U575" t="inlineStr">
+      <c r="X575" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -35957,7 +36172,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U576" t="inlineStr">
+      <c r="X576" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -36015,7 +36230,7 @@
           <t>MAKUBO Sandile</t>
         </is>
       </c>
-      <c r="U577" t="inlineStr">
+      <c r="X577" t="inlineStr">
         <is>
           <t>69119</t>
         </is>
@@ -36073,7 +36288,7 @@
           <t>BERT Michel</t>
         </is>
       </c>
-      <c r="U578" t="inlineStr">
+      <c r="X578" t="inlineStr">
         <is>
           <t>82901</t>
         </is>
@@ -36131,7 +36346,7 @@
           <t>HUMENIUK Vladyslav</t>
         </is>
       </c>
-      <c r="U579" t="inlineStr">
+      <c r="X579" t="inlineStr">
         <is>
           <t>72020</t>
         </is>
@@ -36189,7 +36404,7 @@
           <t>REZANEJAD HASSANJANI Amir</t>
         </is>
       </c>
-      <c r="U580" t="inlineStr">
+      <c r="X580" t="inlineStr">
         <is>
           <t>75398</t>
         </is>
@@ -36247,7 +36462,7 @@
           <t>SARAMANDIF Terence Benjamin</t>
         </is>
       </c>
-      <c r="U581" t="inlineStr">
+      <c r="X581" t="inlineStr">
         <is>
           <t>79340</t>
         </is>
@@ -36305,7 +36520,7 @@
           <t>OZOLS Kriss</t>
         </is>
       </c>
-      <c r="U582" t="inlineStr">
+      <c r="X582" t="inlineStr">
         <is>
           <t>48993</t>
         </is>
@@ -36363,7 +36578,7 @@
           <t>MUSEVYCH Vadym</t>
         </is>
       </c>
-      <c r="U583" t="inlineStr">
+      <c r="X583" t="inlineStr">
         <is>
           <t>35525</t>
         </is>
@@ -36474,7 +36689,7 @@
           <t>CHAKIR Issam</t>
         </is>
       </c>
-      <c r="U585" t="inlineStr">
+      <c r="X585" t="inlineStr">
         <is>
           <t>75631</t>
         </is>
@@ -36532,7 +36747,7 @@
           <t>MAXIMOV Vitaly</t>
         </is>
       </c>
-      <c r="U586" t="inlineStr">
+      <c r="X586" t="inlineStr">
         <is>
           <t>54800</t>
         </is>
@@ -36590,7 +36805,7 @@
           <t>KIM Beomsoo</t>
         </is>
       </c>
-      <c r="U587" t="inlineStr">
+      <c r="X587" t="inlineStr">
         <is>
           <t>64845</t>
         </is>
@@ -36648,7 +36863,7 @@
           <t>ZISEKAS Panagiotis</t>
         </is>
       </c>
-      <c r="U588" t="inlineStr">
+      <c r="X588" t="inlineStr">
         <is>
           <t>64786</t>
         </is>
@@ -36706,7 +36921,7 @@
           <t>AMANBAYEV Adil</t>
         </is>
       </c>
-      <c r="U589" t="inlineStr">
+      <c r="X589" t="inlineStr">
         <is>
           <t>68999</t>
         </is>
@@ -36764,7 +36979,7 @@
           <t>ALVARENGA Frederico</t>
         </is>
       </c>
-      <c r="U590" t="inlineStr">
+      <c r="X590" t="inlineStr">
         <is>
           <t>71976</t>
         </is>
@@ -36822,7 +37037,7 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U591" t="inlineStr">
+      <c r="X591" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -36880,7 +37095,7 @@
           <t>BOURHIS Yves</t>
         </is>
       </c>
-      <c r="U592" t="inlineStr">
+      <c r="X592" t="inlineStr">
         <is>
           <t>63237</t>
         </is>
@@ -36938,7 +37153,7 @@
           <t>CHIARELLO Gelindo</t>
         </is>
       </c>
-      <c r="U593" t="inlineStr">
+      <c r="X593" t="inlineStr">
         <is>
           <t>39956</t>
         </is>
@@ -36996,7 +37211,7 @@
           <t>TEMIRGALIEV Alibek</t>
         </is>
       </c>
-      <c r="U594" t="inlineStr">
+      <c r="X594" t="inlineStr">
         <is>
           <t>61158</t>
         </is>
@@ -37054,7 +37269,7 @@
           <t>LAVIOLETTE Yannick</t>
         </is>
       </c>
-      <c r="U595" t="inlineStr">
+      <c r="X595" t="inlineStr">
         <is>
           <t>43343</t>
         </is>
@@ -37112,7 +37327,7 @@
           <t>HIGGINS Shaun</t>
         </is>
       </c>
-      <c r="U596" t="inlineStr">
+      <c r="X596" t="inlineStr">
         <is>
           <t>36655</t>
         </is>
@@ -37170,7 +37385,7 @@
           <t>LONG Tren</t>
         </is>
       </c>
-      <c r="U597" t="inlineStr">
+      <c r="X597" t="inlineStr">
         <is>
           <t>57124</t>
         </is>
@@ -37228,7 +37443,7 @@
           <t>SILVA Jose</t>
         </is>
       </c>
-      <c r="U598" t="inlineStr">
+      <c r="X598" t="inlineStr">
         <is>
           <t>36494</t>
         </is>
@@ -37286,7 +37501,7 @@
           <t>CHAIDET Yutthakan</t>
         </is>
       </c>
-      <c r="U599" t="inlineStr">
+      <c r="X599" t="inlineStr">
         <is>
           <t>51798</t>
         </is>
@@ -37344,7 +37559,7 @@
           <t>KULIKOV Alexandr</t>
         </is>
       </c>
-      <c r="U600" t="inlineStr">
+      <c r="X600" t="inlineStr">
         <is>
           <t>39679</t>
         </is>
@@ -37402,7 +37617,7 @@
           <t>ZHENG Jiaxin</t>
         </is>
       </c>
-      <c r="U601" t="inlineStr">
+      <c r="X601" t="inlineStr">
         <is>
           <t>75381</t>
         </is>
@@ -37460,7 +37675,7 @@
           <t>COCHRANE Jake</t>
         </is>
       </c>
-      <c r="U602" t="inlineStr">
+      <c r="X602" t="inlineStr">
         <is>
           <t>60124</t>
         </is>
@@ -37518,7 +37733,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U603" t="inlineStr">
+      <c r="X603" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -37576,7 +37791,7 @@
           <t>WASHER Patrick</t>
         </is>
       </c>
-      <c r="U604" t="inlineStr">
+      <c r="X604" t="inlineStr">
         <is>
           <t>42081</t>
         </is>
@@ -37634,7 +37849,7 @@
           <t>POMEROY Spencer</t>
         </is>
       </c>
-      <c r="U605" t="inlineStr">
+      <c r="X605" t="inlineStr">
         <is>
           <t>57783</t>
         </is>
@@ -37692,7 +37907,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U606" t="inlineStr">
+      <c r="X606" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -37750,7 +37965,7 @@
           <t>SASAKI Shota</t>
         </is>
       </c>
-      <c r="U607" t="inlineStr">
+      <c r="X607" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -37808,7 +38023,7 @@
           <t>CURCEL Leonardo</t>
         </is>
       </c>
-      <c r="U608" t="inlineStr">
+      <c r="X608" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
@@ -37866,7 +38081,7 @@
           <t>LHOTA Matyas</t>
         </is>
       </c>
-      <c r="U609" t="inlineStr">
+      <c r="X609" t="inlineStr">
         <is>
           <t>51872</t>
         </is>
@@ -37924,7 +38139,7 @@
           <t>GIBB Benjamin</t>
         </is>
       </c>
-      <c r="U610" t="inlineStr">
+      <c r="X610" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
@@ -37982,7 +38197,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U611" t="inlineStr">
+      <c r="X611" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -38040,7 +38255,7 @@
           <t>SHU Jianming</t>
         </is>
       </c>
-      <c r="U612" t="inlineStr">
+      <c r="X612" t="inlineStr">
         <is>
           <t>47327</t>
         </is>
@@ -38098,7 +38313,7 @@
           <t>CORREA Charles</t>
         </is>
       </c>
-      <c r="U613" t="inlineStr">
+      <c r="X613" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
@@ -38156,7 +38371,7 @@
           <t>SZTUBA Kacper</t>
         </is>
       </c>
-      <c r="U614" t="inlineStr">
+      <c r="X614" t="inlineStr">
         <is>
           <t>53636</t>
         </is>
@@ -38214,7 +38429,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U615" t="inlineStr">
+      <c r="X615" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -38272,7 +38487,7 @@
           <t>CARTER Tristan</t>
         </is>
       </c>
-      <c r="U616" t="inlineStr">
+      <c r="X616" t="inlineStr">
         <is>
           <t>51890</t>
         </is>
@@ -38330,7 +38545,7 @@
           <t>BORGES Felipe</t>
         </is>
       </c>
-      <c r="U617" t="inlineStr">
+      <c r="X617" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
@@ -38388,7 +38603,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U618" t="inlineStr">
+      <c r="X618" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -38446,7 +38661,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U619" t="inlineStr">
+      <c r="X619" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -38504,7 +38719,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U620" t="inlineStr">
+      <c r="X620" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -38562,7 +38777,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U621" t="inlineStr">
+      <c r="X621" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -38620,7 +38835,7 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U622" t="inlineStr">
+      <c r="X622" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -38678,7 +38893,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U623" t="inlineStr">
+      <c r="X623" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -38736,7 +38951,7 @@
           <t>GEBAS Vitezslav</t>
         </is>
       </c>
-      <c r="U624" t="inlineStr">
+      <c r="X624" t="inlineStr">
         <is>
           <t>35038</t>
         </is>
@@ -38794,7 +39009,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U625" t="inlineStr">
+      <c r="X625" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -38852,7 +39067,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U626" t="inlineStr">
+      <c r="X626" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -38910,7 +39125,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U627" t="inlineStr">
+      <c r="X627" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -38968,7 +39183,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U628" t="inlineStr">
+      <c r="X628" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -39026,7 +39241,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U629" t="inlineStr">
+      <c r="X629" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -39084,7 +39299,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U630" t="inlineStr">
+      <c r="X630" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -39142,7 +39357,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U631" t="inlineStr">
+      <c r="X631" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -39215,12 +39430,12 @@
           <t>SHU Jianming</t>
         </is>
       </c>
-      <c r="U632" t="inlineStr">
+      <c r="X632" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
       </c>
-      <c r="V632" t="inlineStr">
+      <c r="Y632" t="inlineStr">
         <is>
           <t>47327</t>
         </is>
@@ -39293,12 +39508,12 @@
           <t>ROISIN Theo</t>
         </is>
       </c>
-      <c r="U633" t="inlineStr">
+      <c r="X633" t="inlineStr">
         <is>
           <t>78746</t>
         </is>
       </c>
-      <c r="V633" t="inlineStr">
+      <c r="Y633" t="inlineStr">
         <is>
           <t>69010</t>
         </is>
@@ -39371,12 +39586,12 @@
           <t>ZHENG Jiaxin</t>
         </is>
       </c>
-      <c r="U634" t="inlineStr">
+      <c r="X634" t="inlineStr">
         <is>
           <t>63801</t>
         </is>
       </c>
-      <c r="V634" t="inlineStr">
+      <c r="Y634" t="inlineStr">
         <is>
           <t>75381</t>
         </is>
@@ -39449,7 +39664,7 @@
           <t>OBRAZTSOV Maxim</t>
         </is>
       </c>
-      <c r="V635" t="inlineStr">
+      <c r="Y635" t="inlineStr">
         <is>
           <t>35767</t>
         </is>
@@ -39522,12 +39737,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U636" t="inlineStr">
+      <c r="X636" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
       </c>
-      <c r="V636" t="inlineStr">
+      <c r="Y636" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -39600,12 +39815,12 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U637" t="inlineStr">
+      <c r="X637" t="inlineStr">
         <is>
           <t>35498</t>
         </is>
       </c>
-      <c r="V637" t="inlineStr">
+      <c r="Y637" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -39678,7 +39893,7 @@
           <t>POCHWALA Marcin</t>
         </is>
       </c>
-      <c r="V638" t="inlineStr">
+      <c r="Y638" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
@@ -39751,12 +39966,12 @@
           <t>MASEK Jan</t>
         </is>
       </c>
-      <c r="U639" t="inlineStr">
+      <c r="X639" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
       </c>
-      <c r="V639" t="inlineStr">
+      <c r="Y639" t="inlineStr">
         <is>
           <t>36013</t>
         </is>
@@ -39829,7 +40044,7 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="V640" t="inlineStr">
+      <c r="Y640" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -39902,12 +40117,12 @@
           <t>PRIGENT Yves</t>
         </is>
       </c>
-      <c r="U641" t="inlineStr">
+      <c r="X641" t="inlineStr">
         <is>
           <t>51995</t>
         </is>
       </c>
-      <c r="V641" t="inlineStr">
+      <c r="Y641" t="inlineStr">
         <is>
           <t>35671</t>
         </is>
@@ -40230,7 +40445,7 @@
           <t>CASTRO PEREIRA Brais</t>
         </is>
       </c>
-      <c r="U647" t="inlineStr">
+      <c r="X647" t="inlineStr">
         <is>
           <t>51851</t>
         </is>
@@ -40293,12 +40508,12 @@
           <t>PEREZ Jesus</t>
         </is>
       </c>
-      <c r="U648" t="inlineStr">
+      <c r="X648" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
       </c>
-      <c r="V648" t="inlineStr">
+      <c r="Y648" t="inlineStr">
         <is>
           <t>36091</t>
         </is>
@@ -40361,12 +40576,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U649" t="inlineStr">
+      <c r="X649" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V649" t="inlineStr">
+      <c r="Y649" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -40487,12 +40702,12 @@
           <t>HOCHSCHORNER Peter</t>
         </is>
       </c>
-      <c r="U651" t="inlineStr">
+      <c r="X651" t="inlineStr">
         <is>
           <t>35356</t>
         </is>
       </c>
-      <c r="V651" t="inlineStr">
+      <c r="Y651" t="inlineStr">
         <is>
           <t>35357</t>
         </is>
@@ -40555,12 +40770,12 @@
           <t>MUELLER Kevin</t>
         </is>
       </c>
-      <c r="U652" t="inlineStr">
+      <c r="X652" t="inlineStr">
         <is>
           <t>35148</t>
         </is>
       </c>
-      <c r="V652" t="inlineStr">
+      <c r="Y652" t="inlineStr">
         <is>
           <t>35149</t>
         </is>
@@ -40623,12 +40838,12 @@
           <t>FERRARI Niccolo</t>
         </is>
       </c>
-      <c r="U653" t="inlineStr">
+      <c r="X653" t="inlineStr">
         <is>
           <t>35497</t>
         </is>
       </c>
-      <c r="V653" t="inlineStr">
+      <c r="Y653" t="inlineStr">
         <is>
           <t>35498</t>
         </is>
@@ -40691,12 +40906,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U654" t="inlineStr">
+      <c r="X654" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V654" t="inlineStr">
+      <c r="Y654" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -40759,12 +40974,12 @@
           <t>WERRO Simon</t>
         </is>
       </c>
-      <c r="U655" t="inlineStr">
+      <c r="X655" t="inlineStr">
         <is>
           <t>35347</t>
         </is>
       </c>
-      <c r="V655" t="inlineStr">
+      <c r="Y655" t="inlineStr">
         <is>
           <t>35424</t>
         </is>
@@ -40827,12 +41042,12 @@
           <t>BENZIEN Jan</t>
         </is>
       </c>
-      <c r="U656" t="inlineStr">
+      <c r="X656" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
       </c>
-      <c r="V656" t="inlineStr">
+      <c r="Y656" t="inlineStr">
         <is>
           <t>35134</t>
         </is>
@@ -40895,12 +41110,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U657" t="inlineStr">
+      <c r="X657" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V657" t="inlineStr">
+      <c r="Y657" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -40963,12 +41178,12 @@
           <t>SZCZEPANSKI Piotr</t>
         </is>
       </c>
-      <c r="U658" t="inlineStr">
+      <c r="X658" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
       </c>
-      <c r="V658" t="inlineStr">
+      <c r="Y658" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
@@ -41031,12 +41246,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U659" t="inlineStr">
+      <c r="X659" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V659" t="inlineStr">
+      <c r="Y659" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -41099,12 +41314,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U660" t="inlineStr">
+      <c r="X660" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V660" t="inlineStr">
+      <c r="Y660" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -41167,12 +41382,12 @@
           <t>CAILHOL Hugo</t>
         </is>
       </c>
-      <c r="U661" t="inlineStr">
+      <c r="X661" t="inlineStr">
         <is>
           <t>35476</t>
         </is>
       </c>
-      <c r="V661" t="inlineStr">
+      <c r="Y661" t="inlineStr">
         <is>
           <t>35491</t>
         </is>
@@ -41235,12 +41450,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U662" t="inlineStr">
+      <c r="X662" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V662" t="inlineStr">
+      <c r="Y662" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -41303,12 +41518,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U663" t="inlineStr">
+      <c r="X663" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V663" t="inlineStr">
+      <c r="Y663" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -41371,12 +41586,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U664" t="inlineStr">
+      <c r="X664" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V664" t="inlineStr">
+      <c r="Y664" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -41434,7 +41649,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U665" t="inlineStr">
+      <c r="X665" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -41492,7 +41707,7 @@
           <t>SKACHOVA Monika</t>
         </is>
       </c>
-      <c r="U666" t="inlineStr">
+      <c r="X666" t="inlineStr">
         <is>
           <t>53078</t>
         </is>
@@ -41550,7 +41765,7 @@
           <t>SABITOVA Zulfia</t>
         </is>
       </c>
-      <c r="U667" t="inlineStr">
+      <c r="X667" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -41608,7 +41823,7 @@
           <t>XU Yanru</t>
         </is>
       </c>
-      <c r="U668" t="inlineStr">
+      <c r="X668" t="inlineStr">
         <is>
           <t>63801</t>
         </is>
@@ -41719,7 +41934,7 @@
           <t>BIZJAK Nina</t>
         </is>
       </c>
-      <c r="U670" t="inlineStr">
+      <c r="X670" t="inlineStr">
         <is>
           <t>39984</t>
         </is>
@@ -41777,7 +41992,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U671" t="inlineStr">
+      <c r="X671" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -41835,7 +42050,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U672" t="inlineStr">
+      <c r="X672" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -41893,7 +42108,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U673" t="inlineStr">
+      <c r="X673" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -41951,7 +42166,7 @@
           <t>GIBSON Eilidh</t>
         </is>
       </c>
-      <c r="U674" t="inlineStr">
+      <c r="X674" t="inlineStr">
         <is>
           <t>36708</t>
         </is>
@@ -42009,7 +42224,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U675" t="inlineStr">
+      <c r="X675" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -42067,7 +42282,7 @@
           <t>MUKHGALEEVA Polina</t>
         </is>
       </c>
-      <c r="U676" t="inlineStr">
+      <c r="X676" t="inlineStr">
         <is>
           <t>35768</t>
         </is>
@@ -42178,7 +42393,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U678" t="inlineStr">
+      <c r="X678" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -42236,7 +42451,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U679" t="inlineStr">
+      <c r="X679" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -42294,7 +42509,7 @@
           <t>HERZOG Andrea</t>
         </is>
       </c>
-      <c r="U680" t="inlineStr">
+      <c r="X680" t="inlineStr">
         <is>
           <t>55099</t>
         </is>
@@ -42352,7 +42567,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U681" t="inlineStr">
+      <c r="X681" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -42410,7 +42625,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U682" t="inlineStr">
+      <c r="X682" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -42468,7 +42683,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U683" t="inlineStr">
+      <c r="X683" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -42526,7 +42741,7 @@
           <t>VAN DER KNIJFF Annebel</t>
         </is>
       </c>
-      <c r="U684" t="inlineStr">
+      <c r="X684" t="inlineStr">
         <is>
           <t>39945</t>
         </is>
@@ -42584,7 +42799,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U685" t="inlineStr">
+      <c r="X685" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -42695,7 +42910,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U687" t="inlineStr">
+      <c r="X687" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -42753,7 +42968,7 @@
           <t>RIHOVA Eva</t>
         </is>
       </c>
-      <c r="U688" t="inlineStr">
+      <c r="X688" t="inlineStr">
         <is>
           <t>51791</t>
         </is>
@@ -42811,7 +43026,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U689" t="inlineStr">
+      <c r="X689" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -42869,7 +43084,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U690" t="inlineStr">
+      <c r="X690" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -42927,7 +43142,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U691" t="inlineStr">
+      <c r="X691" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -42985,7 +43200,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U692" t="inlineStr">
+      <c r="X692" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -43043,7 +43258,7 @@
           <t>JACQUET Claire</t>
         </is>
       </c>
-      <c r="U693" t="inlineStr">
+      <c r="X693" t="inlineStr">
         <is>
           <t>35684</t>
         </is>
@@ -43101,7 +43316,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U694" t="inlineStr">
+      <c r="X694" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -43159,7 +43374,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U695" t="inlineStr">
+      <c r="X695" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -43217,7 +43432,7 @@
           <t>SCHWEIKERT Fabian</t>
         </is>
       </c>
-      <c r="U696" t="inlineStr">
+      <c r="X696" t="inlineStr">
         <is>
           <t>38412</t>
         </is>
@@ -43275,7 +43490,7 @@
           <t>JAKSE Zan</t>
         </is>
       </c>
-      <c r="U697" t="inlineStr">
+      <c r="X697" t="inlineStr">
         <is>
           <t>44340</t>
         </is>
@@ -43333,7 +43548,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U698" t="inlineStr">
+      <c r="X698" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -43391,7 +43606,7 @@
           <t>IVALDI Zeno</t>
         </is>
       </c>
-      <c r="U699" t="inlineStr">
+      <c r="X699" t="inlineStr">
         <is>
           <t>35480</t>
         </is>
@@ -43449,7 +43664,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U700" t="inlineStr">
+      <c r="X700" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -43507,7 +43722,7 @@
           <t>LAUNAY Antoine</t>
         </is>
       </c>
-      <c r="U701" t="inlineStr">
+      <c r="X701" t="inlineStr">
         <is>
           <t>68776</t>
         </is>
@@ -43565,7 +43780,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U702" t="inlineStr">
+      <c r="X702" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -43623,7 +43838,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U703" t="inlineStr">
+      <c r="X703" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -43681,7 +43896,7 @@
           <t>COMBOT Sebastien</t>
         </is>
       </c>
-      <c r="U704" t="inlineStr">
+      <c r="X704" t="inlineStr">
         <is>
           <t>35234</t>
         </is>
@@ -43739,7 +43954,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U705" t="inlineStr">
+      <c r="X705" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -43797,7 +44012,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U706" t="inlineStr">
+      <c r="X706" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -43855,7 +44070,7 @@
           <t>HOLMER Erik</t>
         </is>
       </c>
-      <c r="U707" t="inlineStr">
+      <c r="X707" t="inlineStr">
         <is>
           <t>35104</t>
         </is>
@@ -43913,7 +44128,7 @@
           <t>GRIGAR Jakub</t>
         </is>
       </c>
-      <c r="U708" t="inlineStr">
+      <c r="X708" t="inlineStr">
         <is>
           <t>37284</t>
         </is>
@@ -43971,7 +44186,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U709" t="inlineStr">
+      <c r="X709" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -44029,7 +44244,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U710" t="inlineStr">
+      <c r="X710" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -44087,7 +44302,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U711" t="inlineStr">
+      <c r="X711" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -44145,7 +44360,7 @@
           <t>WEGER Matthias</t>
         </is>
       </c>
-      <c r="U712" t="inlineStr">
+      <c r="X712" t="inlineStr">
         <is>
           <t>68837</t>
         </is>
@@ -44203,7 +44418,7 @@
           <t>YAZAWA Kazuki</t>
         </is>
       </c>
-      <c r="U713" t="inlineStr">
+      <c r="X713" t="inlineStr">
         <is>
           <t>36482</t>
         </is>
@@ -44261,7 +44476,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U714" t="inlineStr">
+      <c r="X714" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -44319,7 +44534,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U715" t="inlineStr">
+      <c r="X715" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -44377,7 +44592,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U716" t="inlineStr">
+      <c r="X716" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -44435,7 +44650,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U717" t="inlineStr">
+      <c r="X717" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -44493,7 +44708,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U718" t="inlineStr">
+      <c r="X718" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -44551,7 +44766,7 @@
           <t>DAWSON Mike</t>
         </is>
       </c>
-      <c r="U719" t="inlineStr">
+      <c r="X719" t="inlineStr">
         <is>
           <t>36656</t>
         </is>
@@ -44609,7 +44824,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U720" t="inlineStr">
+      <c r="X720" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -44667,7 +44882,7 @@
           <t>BIAZIZZO Mathieu</t>
         </is>
       </c>
-      <c r="U721" t="inlineStr">
+      <c r="X721" t="inlineStr">
         <is>
           <t>35484</t>
         </is>
@@ -44725,7 +44940,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U722" t="inlineStr">
+      <c r="X722" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -44783,7 +44998,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U723" t="inlineStr">
+      <c r="X723" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -44841,7 +45056,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U724" t="inlineStr">
+      <c r="X724" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -44899,7 +45114,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U725" t="inlineStr">
+      <c r="X725" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -44957,7 +45172,7 @@
           <t>MALEK Andrej</t>
         </is>
       </c>
-      <c r="U726" t="inlineStr">
+      <c r="X726" t="inlineStr">
         <is>
           <t>39246</t>
         </is>
@@ -45015,7 +45230,7 @@
           <t>BOWERS Christopher</t>
         </is>
       </c>
-      <c r="U727" t="inlineStr">
+      <c r="X727" t="inlineStr">
         <is>
           <t>52010</t>
         </is>
@@ -45073,7 +45288,7 @@
           <t>WEGER Jakob</t>
         </is>
       </c>
-      <c r="U728" t="inlineStr">
+      <c r="X728" t="inlineStr">
         <is>
           <t>54909</t>
         </is>
@@ -45131,7 +45346,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U729" t="inlineStr">
+      <c r="X729" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -45242,7 +45457,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U731" t="inlineStr">
+      <c r="X731" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -45300,7 +45515,7 @@
           <t>HERNANZ Samuel</t>
         </is>
       </c>
-      <c r="U732" t="inlineStr">
+      <c r="X732" t="inlineStr">
         <is>
           <t>35786</t>
         </is>
@@ -45358,7 +45573,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U733" t="inlineStr">
+      <c r="X733" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -45416,7 +45631,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U734" t="inlineStr">
+      <c r="X734" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -45489,12 +45704,12 @@
           <t>PEREZ Jesus</t>
         </is>
       </c>
-      <c r="U735" t="inlineStr">
+      <c r="X735" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
       </c>
-      <c r="V735" t="inlineStr">
+      <c r="Y735" t="inlineStr">
         <is>
           <t>36091</t>
         </is>
@@ -45567,12 +45782,12 @@
           <t>FERRARI Niccolo</t>
         </is>
       </c>
-      <c r="U736" t="inlineStr">
+      <c r="X736" t="inlineStr">
         <is>
           <t>35497</t>
         </is>
       </c>
-      <c r="V736" t="inlineStr">
+      <c r="Y736" t="inlineStr">
         <is>
           <t>35498</t>
         </is>
@@ -45645,12 +45860,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U737" t="inlineStr">
+      <c r="X737" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V737" t="inlineStr">
+      <c r="Y737" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -45723,12 +45938,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U738" t="inlineStr">
+      <c r="X738" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V738" t="inlineStr">
+      <c r="Y738" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -45801,12 +46016,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U739" t="inlineStr">
+      <c r="X739" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V739" t="inlineStr">
+      <c r="Y739" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -45879,12 +46094,12 @@
           <t>HOCHSCHORNER Peter</t>
         </is>
       </c>
-      <c r="U740" t="inlineStr">
+      <c r="X740" t="inlineStr">
         <is>
           <t>35356</t>
         </is>
       </c>
-      <c r="V740" t="inlineStr">
+      <c r="Y740" t="inlineStr">
         <is>
           <t>35357</t>
         </is>
@@ -45957,12 +46172,12 @@
           <t>SZCZEPANSKI Piotr</t>
         </is>
       </c>
-      <c r="U741" t="inlineStr">
+      <c r="X741" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
       </c>
-      <c r="V741" t="inlineStr">
+      <c r="Y741" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
@@ -46035,12 +46250,12 @@
           <t>CAILHOL Hugo</t>
         </is>
       </c>
-      <c r="U742" t="inlineStr">
+      <c r="X742" t="inlineStr">
         <is>
           <t>35476</t>
         </is>
       </c>
-      <c r="V742" t="inlineStr">
+      <c r="Y742" t="inlineStr">
         <is>
           <t>35491</t>
         </is>
@@ -46113,12 +46328,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U743" t="inlineStr">
+      <c r="X743" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V743" t="inlineStr">
+      <c r="Y743" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -46191,12 +46406,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U744" t="inlineStr">
+      <c r="X744" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V744" t="inlineStr">
+      <c r="Y744" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -46264,7 +46479,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U745" t="inlineStr">
+      <c r="X745" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -46332,7 +46547,7 @@
           <t>SABITOVA Zulfia</t>
         </is>
       </c>
-      <c r="U746" t="inlineStr">
+      <c r="X746" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -46400,7 +46615,7 @@
           <t>MUKHGALEEVA Polina</t>
         </is>
       </c>
-      <c r="U747" t="inlineStr">
+      <c r="X747" t="inlineStr">
         <is>
           <t>35768</t>
         </is>
@@ -46468,7 +46683,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U748" t="inlineStr">
+      <c r="X748" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -46536,7 +46751,7 @@
           <t>PRIOUX Lucie</t>
         </is>
       </c>
-      <c r="U749" t="inlineStr">
+      <c r="X749" t="inlineStr">
         <is>
           <t>42984</t>
         </is>
@@ -46604,7 +46819,7 @@
           <t>GIBSON Eilidh</t>
         </is>
       </c>
-      <c r="U750" t="inlineStr">
+      <c r="X750" t="inlineStr">
         <is>
           <t>36708</t>
         </is>
@@ -46672,7 +46887,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U751" t="inlineStr">
+      <c r="X751" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -46740,7 +46955,7 @@
           <t>WOODS Kimberley</t>
         </is>
       </c>
-      <c r="U752" t="inlineStr">
+      <c r="X752" t="inlineStr">
         <is>
           <t>35650</t>
         </is>
@@ -46871,7 +47086,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U754" t="inlineStr">
+      <c r="X754" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -46939,7 +47154,7 @@
           <t>DAWSON Mike</t>
         </is>
       </c>
-      <c r="U755" t="inlineStr">
+      <c r="X755" t="inlineStr">
         <is>
           <t>36656</t>
         </is>
@@ -47007,7 +47222,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U756" t="inlineStr">
+      <c r="X756" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -47075,7 +47290,7 @@
           <t>SRABOTNIK Martin</t>
         </is>
       </c>
-      <c r="U757" t="inlineStr">
+      <c r="X757" t="inlineStr">
         <is>
           <t>39080</t>
         </is>
@@ -47143,7 +47358,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U758" t="inlineStr">
+      <c r="X758" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -47211,7 +47426,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U759" t="inlineStr">
+      <c r="X759" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -47279,7 +47494,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U760" t="inlineStr">
+      <c r="X760" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -47347,7 +47562,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U761" t="inlineStr">
+      <c r="X761" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -47415,7 +47630,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U762" t="inlineStr">
+      <c r="X762" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -47483,7 +47698,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U763" t="inlineStr">
+      <c r="X763" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -47551,7 +47766,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U764" t="inlineStr">
+      <c r="X764" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -47821,7 +48036,7 @@
           <t>FRANKLIN Mallory</t>
         </is>
       </c>
-      <c r="U769" t="inlineStr">
+      <c r="X769" t="inlineStr">
         <is>
           <t>35615</t>
         </is>
@@ -47879,7 +48094,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U770" t="inlineStr">
+      <c r="X770" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -47937,7 +48152,7 @@
           <t>REN Ye</t>
         </is>
       </c>
-      <c r="U771" t="inlineStr">
+      <c r="X771" t="inlineStr">
         <is>
           <t>68810</t>
         </is>
@@ -47995,7 +48210,7 @@
           <t>LI Tong</t>
         </is>
       </c>
-      <c r="U772" t="inlineStr">
+      <c r="X772" t="inlineStr">
         <is>
           <t>52023</t>
         </is>
@@ -48053,7 +48268,7 @@
           <t>MEDON Joanna</t>
         </is>
       </c>
-      <c r="U773" t="inlineStr">
+      <c r="X773" t="inlineStr">
         <is>
           <t>35438</t>
         </is>
@@ -48111,7 +48326,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U774" t="inlineStr">
+      <c r="X774" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -48169,7 +48384,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U775" t="inlineStr">
+      <c r="X775" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -48227,7 +48442,7 @@
           <t>GOIKOETXEA Irati</t>
         </is>
       </c>
-      <c r="U776" t="inlineStr">
+      <c r="X776" t="inlineStr">
         <is>
           <t>35761</t>
         </is>
@@ -48285,7 +48500,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U777" t="inlineStr">
+      <c r="X777" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -48343,7 +48558,7 @@
           <t>KHARITONOVA Marta</t>
         </is>
       </c>
-      <c r="U778" t="inlineStr">
+      <c r="X778" t="inlineStr">
         <is>
           <t>35257</t>
         </is>
@@ -48401,7 +48616,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U779" t="inlineStr">
+      <c r="X779" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -48459,7 +48674,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U780" t="inlineStr">
+      <c r="X780" t="inlineStr">
         <is>
           <t>35231</t>
         </is>
@@ -48517,7 +48732,7 @@
           <t>KALISKA Elena</t>
         </is>
       </c>
-      <c r="U781" t="inlineStr">
+      <c r="X781" t="inlineStr">
         <is>
           <t>35366</t>
         </is>
@@ -48575,7 +48790,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U782" t="inlineStr">
+      <c r="X782" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -48633,7 +48848,7 @@
           <t>ZWOLINSKA Klaudia</t>
         </is>
       </c>
-      <c r="U783" t="inlineStr">
+      <c r="X783" t="inlineStr">
         <is>
           <t>42027</t>
         </is>
@@ -48691,7 +48906,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U784" t="inlineStr">
+      <c r="X784" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -48749,7 +48964,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U785" t="inlineStr">
+      <c r="X785" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -48807,7 +49022,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U786" t="inlineStr">
+      <c r="X786" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -48865,7 +49080,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U787" t="inlineStr">
+      <c r="X787" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -48923,7 +49138,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U788" t="inlineStr">
+      <c r="X788" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -48981,7 +49196,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U789" t="inlineStr">
+      <c r="X789" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -49039,7 +49254,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U790" t="inlineStr">
+      <c r="X790" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -49097,7 +49312,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U791" t="inlineStr">
+      <c r="X791" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -49155,7 +49370,7 @@
           <t>PEROVA Ekaterina</t>
         </is>
       </c>
-      <c r="U792" t="inlineStr">
+      <c r="X792" t="inlineStr">
         <is>
           <t>35131</t>
         </is>
@@ -49213,7 +49428,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U793" t="inlineStr">
+      <c r="X793" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -49271,7 +49486,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U794" t="inlineStr">
+      <c r="X794" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -49329,7 +49544,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U795" t="inlineStr">
+      <c r="X795" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -49387,7 +49602,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U796" t="inlineStr">
+      <c r="X796" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -49445,7 +49660,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U797" t="inlineStr">
+      <c r="X797" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -49503,7 +49718,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U798" t="inlineStr">
+      <c r="X798" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -49561,7 +49776,7 @@
           <t>GEBAS Vitezslav</t>
         </is>
       </c>
-      <c r="U799" t="inlineStr">
+      <c r="X799" t="inlineStr">
         <is>
           <t>35038</t>
         </is>
@@ -49619,7 +49834,7 @@
           <t>BORGES Felipe</t>
         </is>
       </c>
-      <c r="U800" t="inlineStr">
+      <c r="X800" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
@@ -49677,7 +49892,7 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U801" t="inlineStr">
+      <c r="X801" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -49735,7 +49950,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U802" t="inlineStr">
+      <c r="X802" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -49793,7 +50008,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U803" t="inlineStr">
+      <c r="X803" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -49851,7 +50066,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U804" t="inlineStr">
+      <c r="X804" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -49909,7 +50124,7 @@
           <t>BOURHIS Yves</t>
         </is>
       </c>
-      <c r="U805" t="inlineStr">
+      <c r="X805" t="inlineStr">
         <is>
           <t>63237</t>
         </is>
@@ -49967,7 +50182,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U806" t="inlineStr">
+      <c r="X806" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -50025,7 +50240,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U807" t="inlineStr">
+      <c r="X807" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -50083,7 +50298,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U808" t="inlineStr">
+      <c r="X808" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -50141,7 +50356,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U809" t="inlineStr">
+      <c r="X809" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -50199,7 +50414,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U810" t="inlineStr">
+      <c r="X810" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -50257,7 +50472,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U811" t="inlineStr">
+      <c r="X811" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -50315,7 +50530,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U812" t="inlineStr">
+      <c r="X812" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -50373,7 +50588,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U813" t="inlineStr">
+      <c r="X813" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -50431,7 +50646,7 @@
           <t>MARZO Daniel</t>
         </is>
       </c>
-      <c r="U814" t="inlineStr">
+      <c r="X814" t="inlineStr">
         <is>
           <t>35757</t>
         </is>
@@ -50489,7 +50704,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U815" t="inlineStr">
+      <c r="X815" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -50547,7 +50762,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U816" t="inlineStr">
+      <c r="X816" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -50605,7 +50820,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U817" t="inlineStr">
+      <c r="X817" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -50663,7 +50878,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U818" t="inlineStr">
+      <c r="X818" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -50721,7 +50936,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U819" t="inlineStr">
+      <c r="X819" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -50779,7 +50994,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U820" t="inlineStr">
+      <c r="X820" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -50837,7 +51052,7 @@
           <t>SETKIN Kirill</t>
         </is>
       </c>
-      <c r="U821" t="inlineStr">
+      <c r="X821" t="inlineStr">
         <is>
           <t>35457</t>
         </is>
@@ -50895,7 +51110,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U822" t="inlineStr">
+      <c r="X822" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -50953,7 +51168,7 @@
           <t>SZCZEPANSKI Piotr</t>
         </is>
       </c>
-      <c r="U823" t="inlineStr">
+      <c r="X823" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
@@ -51011,7 +51226,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U824" t="inlineStr">
+      <c r="X824" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -51069,7 +51284,7 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U825" t="inlineStr">
+      <c r="X825" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -51127,7 +51342,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U826" t="inlineStr">
+      <c r="X826" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -51185,7 +51400,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U827" t="inlineStr">
+      <c r="X827" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -51243,7 +51458,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U828" t="inlineStr">
+      <c r="X828" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -51311,7 +51526,7 @@
           <t>FOX Jessica</t>
         </is>
       </c>
-      <c r="U829" t="inlineStr">
+      <c r="X829" t="inlineStr">
         <is>
           <t>36526</t>
         </is>
@@ -51379,7 +51594,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U830" t="inlineStr">
+      <c r="X830" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -51447,7 +51662,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U831" t="inlineStr">
+      <c r="X831" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -51515,7 +51730,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U832" t="inlineStr">
+      <c r="X832" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -51583,7 +51798,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U833" t="inlineStr">
+      <c r="X833" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -51651,7 +51866,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U834" t="inlineStr">
+      <c r="X834" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -51719,7 +51934,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U835" t="inlineStr">
+      <c r="X835" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -51787,7 +52002,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U836" t="inlineStr">
+      <c r="X836" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -51855,7 +52070,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U837" t="inlineStr">
+      <c r="X837" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -51923,7 +52138,7 @@
           <t>PENNIE Fiona</t>
         </is>
       </c>
-      <c r="U838" t="inlineStr">
+      <c r="X838" t="inlineStr">
         <is>
           <t>35638</t>
         </is>
@@ -51991,7 +52206,7 @@
           <t>ELOSEGI Ander</t>
         </is>
       </c>
-      <c r="U839" t="inlineStr">
+      <c r="X839" t="inlineStr">
         <is>
           <t>35785</t>
         </is>
@@ -52059,7 +52274,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U840" t="inlineStr">
+      <c r="X840" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -52127,7 +52342,7 @@
           <t>LE RUYET Edern</t>
         </is>
       </c>
-      <c r="U841" t="inlineStr">
+      <c r="X841" t="inlineStr">
         <is>
           <t>35379</t>
         </is>
@@ -52195,7 +52410,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U842" t="inlineStr">
+      <c r="X842" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -52263,7 +52478,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U843" t="inlineStr">
+      <c r="X843" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -52331,7 +52546,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U844" t="inlineStr">
+      <c r="X844" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -52399,7 +52614,7 @@
           <t>COLAZINGARI Roberto</t>
         </is>
       </c>
-      <c r="U845" t="inlineStr">
+      <c r="X845" t="inlineStr">
         <is>
           <t>35223</t>
         </is>
@@ -52467,7 +52682,7 @@
           <t>MARTIKAN Michal</t>
         </is>
       </c>
-      <c r="U846" t="inlineStr">
+      <c r="X846" t="inlineStr">
         <is>
           <t>35365</t>
         </is>
@@ -52535,7 +52750,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U847" t="inlineStr">
+      <c r="X847" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -52603,7 +52818,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U848" t="inlineStr">
+      <c r="X848" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -52671,7 +52886,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U849" t="inlineStr">
+      <c r="X849" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
